--- a/source/Inventory_Master_V7.xlsx
+++ b/source/Inventory_Master_V7.xlsx
@@ -836,7 +836,11 @@
           <t>V4629</t>
         </is>
       </c>
-      <c r="F2" s="11" t="n"/>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>152-11-4</t>
+        </is>
+      </c>
       <c r="G2" s="9" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
@@ -974,7 +978,11 @@
           <t>237329</t>
         </is>
       </c>
-      <c r="F4" s="11" t="n"/>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>97-00-7</t>
+        </is>
+      </c>
       <c r="G4" s="9" t="n"/>
       <c r="H4" s="12" t="inlineStr">
         <is>
@@ -1108,7 +1116,11 @@
           <t>78641</t>
         </is>
       </c>
-      <c r="F6" s="11" t="n"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>7786-30-3</t>
+        </is>
+      </c>
       <c r="G6" s="9" t="n"/>
       <c r="H6" s="12" t="inlineStr">
         <is>
@@ -1400,7 +1412,11 @@
           <t>1.09634.1011</t>
         </is>
       </c>
-      <c r="F10" s="11" t="n"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>67-63-0</t>
+        </is>
+      </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="12" t="inlineStr">
         <is>
@@ -1479,7 +1495,11 @@
           <t>4250-050-04</t>
         </is>
       </c>
-      <c r="F11" s="11" t="n"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>60-00-4</t>
+        </is>
+      </c>
       <c r="G11" s="15" t="n"/>
       <c r="H11" s="12" t="inlineStr">
         <is>
@@ -1550,7 +1570,11 @@
           <t>D9628</t>
         </is>
       </c>
-      <c r="F12" s="11" t="n"/>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>59-92-7</t>
+        </is>
+      </c>
       <c r="G12" s="9" t="n"/>
       <c r="H12" s="12" t="inlineStr">
         <is>
@@ -1617,7 +1641,11 @@
           <t>D0550</t>
         </is>
       </c>
-      <c r="F13" s="11" t="n"/>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>609-99-4</t>
+        </is>
+      </c>
       <c r="G13" s="15" t="n"/>
       <c r="H13" s="12" t="inlineStr">
         <is>
@@ -1684,7 +1712,11 @@
           <t>382051</t>
         </is>
       </c>
-      <c r="F14" s="11" t="n"/>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>458-36-6</t>
+        </is>
+      </c>
       <c r="G14" s="9" t="n"/>
       <c r="H14" s="12" t="inlineStr">
         <is>
@@ -1830,7 +1862,11 @@
           <t>A79809</t>
         </is>
       </c>
-      <c r="F16" s="11" t="n"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>89-57-6</t>
+        </is>
+      </c>
       <c r="G16" s="9" t="n"/>
       <c r="H16" s="12" t="inlineStr">
         <is>
@@ -2098,7 +2134,11 @@
           <t>270725</t>
         </is>
       </c>
-      <c r="F20" s="11" t="n"/>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>67-64-1</t>
+        </is>
+      </c>
       <c r="G20" s="9" t="n"/>
       <c r="H20" s="12" t="inlineStr">
         <is>
@@ -2169,7 +2209,11 @@
           <t>A998-4</t>
         </is>
       </c>
-      <c r="F21" s="11" t="n"/>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>75-05-8</t>
+        </is>
+      </c>
       <c r="G21" s="15" t="n"/>
       <c r="H21" s="12" t="inlineStr">
         <is>
@@ -2441,7 +2485,11 @@
           <t>A5533</t>
         </is>
       </c>
-      <c r="F25" s="11" t="n"/>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>83-61-4</t>
+        </is>
+      </c>
       <c r="G25" s="15" t="n"/>
       <c r="H25" s="12" t="inlineStr">
         <is>
@@ -2508,7 +2556,11 @@
           <t>237051</t>
         </is>
       </c>
-      <c r="F26" s="11" t="n"/>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>7446-70-0</t>
+        </is>
+      </c>
       <c r="G26" s="9" t="n"/>
       <c r="H26" s="12" t="inlineStr">
         <is>
@@ -2575,7 +2627,11 @@
           <t>A3678</t>
         </is>
       </c>
-      <c r="F27" s="11" t="n"/>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>7727-54-0</t>
+        </is>
+      </c>
       <c r="G27" s="15" t="n"/>
       <c r="H27" s="12" t="inlineStr">
         <is>
@@ -2709,7 +2765,11 @@
           <t>243671</t>
         </is>
       </c>
-      <c r="F29" s="11" t="n"/>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>543-80-6</t>
+        </is>
+      </c>
       <c r="G29" s="15" t="n"/>
       <c r="H29" s="12" t="inlineStr">
         <is>
@@ -2776,7 +2836,11 @@
           <t>PHR1502</t>
         </is>
       </c>
-      <c r="F30" s="11" t="n"/>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>633-65-8</t>
+        </is>
+      </c>
       <c r="G30" s="9" t="n"/>
       <c r="H30" s="12" t="inlineStr">
         <is>
@@ -2843,7 +2907,11 @@
           <t>B3251</t>
         </is>
       </c>
-      <c r="F31" s="11" t="n"/>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>633-65-8</t>
+        </is>
+      </c>
       <c r="G31" s="15" t="n"/>
       <c r="H31" s="12" t="inlineStr">
         <is>
@@ -2914,7 +2982,11 @@
           <t>B0397</t>
         </is>
       </c>
-      <c r="F32" s="11" t="n"/>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>7659-95-2</t>
+        </is>
+      </c>
       <c r="G32" s="9" t="n"/>
       <c r="H32" s="12" t="inlineStr">
         <is>
@@ -2981,7 +3053,11 @@
           <t>C0625</t>
         </is>
       </c>
-      <c r="F33" s="11" t="n"/>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>331-39-5</t>
+        </is>
+      </c>
       <c r="G33" s="15" t="n"/>
       <c r="H33" s="12" t="inlineStr">
         <is>
@@ -3052,7 +3128,11 @@
           <t>117960(12531)</t>
         </is>
       </c>
-      <c r="F34" s="11" t="n"/>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>10035-04-8</t>
+        </is>
+      </c>
       <c r="G34" s="9" t="n"/>
       <c r="H34" s="12" t="inlineStr">
         <is>
@@ -3119,7 +3199,11 @@
           <t>C3618</t>
         </is>
       </c>
-      <c r="F35" s="11" t="n"/>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>83881-52-1</t>
+        </is>
+      </c>
       <c r="G35" s="15" t="n"/>
       <c r="H35" s="12" t="inlineStr">
         <is>
@@ -3186,7 +3270,11 @@
           <t>C0732</t>
         </is>
       </c>
-      <c r="F36" s="11" t="n"/>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>123-03-5</t>
+        </is>
+      </c>
       <c r="G36" s="9" t="n"/>
       <c r="H36" s="12" t="inlineStr">
         <is>
@@ -3253,7 +3341,11 @@
           <t>SC-204681</t>
         </is>
       </c>
-      <c r="F37" s="11" t="n"/>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>94-41-7</t>
+        </is>
+      </c>
       <c r="G37" s="15" t="n"/>
       <c r="H37" s="12" t="inlineStr">
         <is>
@@ -3320,7 +3412,11 @@
           <t>C2432</t>
         </is>
       </c>
-      <c r="F38" s="11" t="n"/>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>67-66-3</t>
+        </is>
+      </c>
       <c r="G38" s="9" t="n"/>
       <c r="H38" s="12" t="inlineStr">
         <is>
@@ -3387,7 +3483,11 @@
           <t>C3878</t>
         </is>
       </c>
-      <c r="F39" s="11" t="n"/>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>327-97-9</t>
+        </is>
+      </c>
       <c r="G39" s="15" t="n"/>
       <c r="H39" s="12" t="inlineStr">
         <is>
@@ -3521,7 +3621,11 @@
           <t>232696</t>
         </is>
       </c>
-      <c r="F41" s="11" t="n"/>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>7440-48-4</t>
+        </is>
+      </c>
       <c r="G41" s="15" t="n"/>
       <c r="H41" s="12" t="inlineStr">
         <is>
@@ -3663,7 +3767,11 @@
           <t>47249</t>
         </is>
       </c>
-      <c r="F43" s="11" t="n"/>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>58367-01-4</t>
+        </is>
+      </c>
       <c r="G43" s="15" t="n"/>
       <c r="H43" s="12" t="inlineStr">
         <is>
@@ -3722,7 +3830,11 @@
           <t>G5767</t>
         </is>
       </c>
-      <c r="F44" s="11" t="n"/>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>58367-01-4</t>
+        </is>
+      </c>
       <c r="G44" s="9" t="n"/>
       <c r="H44" s="12" t="inlineStr">
         <is>
@@ -3789,7 +3901,11 @@
           <t>F2793</t>
         </is>
       </c>
-      <c r="F45" s="11" t="n"/>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>30237-26-4</t>
+        </is>
+      </c>
       <c r="G45" s="15" t="n"/>
       <c r="H45" s="12" t="inlineStr">
         <is>
@@ -3990,7 +4106,11 @@
           <t>3030-4400</t>
         </is>
       </c>
-      <c r="F48" s="11" t="n"/>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>75-09-2</t>
+        </is>
+      </c>
       <c r="G48" s="9" t="n"/>
       <c r="H48" s="12" t="inlineStr">
         <is>
@@ -4057,7 +4177,11 @@
           <t>31589</t>
         </is>
       </c>
-      <c r="F49" s="11" t="n"/>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>111-42-2</t>
+        </is>
+      </c>
       <c r="G49" s="15" t="n"/>
       <c r="H49" s="12" t="inlineStr">
         <is>
@@ -4258,7 +4382,11 @@
           <t>D3281</t>
         </is>
       </c>
-      <c r="F52" s="11" t="n"/>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>22494-42-4</t>
+        </is>
+      </c>
       <c r="G52" s="9" t="n"/>
       <c r="H52" s="12" t="inlineStr">
         <is>
@@ -4325,7 +4453,11 @@
           <t>D8418</t>
         </is>
       </c>
-      <c r="F53" s="11" t="n"/>
+      <c r="F53" s="11" t="inlineStr">
+        <is>
+          <t>67-68-5</t>
+        </is>
+      </c>
       <c r="G53" s="15" t="n"/>
       <c r="H53" s="12" t="inlineStr">
         <is>
@@ -4392,7 +4524,11 @@
           <t>3047-4400</t>
         </is>
       </c>
-      <c r="F54" s="11" t="n"/>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>67-68-5</t>
+        </is>
+      </c>
       <c r="G54" s="9" t="n"/>
       <c r="H54" s="12" t="inlineStr">
         <is>
@@ -4526,7 +4662,11 @@
           <t>1.00983.1011</t>
         </is>
       </c>
-      <c r="F56" s="11" t="n"/>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>64-17-5</t>
+        </is>
+      </c>
       <c r="G56" s="9" t="n"/>
       <c r="H56" s="12" t="inlineStr">
         <is>
@@ -4593,7 +4733,11 @@
           <t>54-17-5</t>
         </is>
       </c>
-      <c r="F57" s="11" t="n"/>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>64-17-5</t>
+        </is>
+      </c>
       <c r="G57" s="15" t="n"/>
       <c r="H57" s="12" t="inlineStr">
         <is>
@@ -4660,7 +4804,11 @@
           <t>E0219</t>
         </is>
       </c>
-      <c r="F58" s="11" t="n"/>
+      <c r="F58" s="11" t="inlineStr">
+        <is>
+          <t>64-17-5</t>
+        </is>
+      </c>
       <c r="G58" s="9" t="n"/>
       <c r="H58" s="12" t="inlineStr">
         <is>
@@ -4794,7 +4942,11 @@
           <t>E1383</t>
         </is>
       </c>
-      <c r="F60" s="11" t="n"/>
+      <c r="F60" s="11" t="inlineStr">
+        <is>
+          <t>33419-42-0</t>
+        </is>
+      </c>
       <c r="G60" s="9" t="n"/>
       <c r="H60" s="12" t="inlineStr">
         <is>
@@ -5074,7 +5226,11 @@
           <t>F7508</t>
         </is>
       </c>
-      <c r="F64" s="11" t="n"/>
+      <c r="F64" s="11" t="inlineStr">
+        <is>
+          <t>75-12-7</t>
+        </is>
+      </c>
       <c r="G64" s="9" t="n"/>
       <c r="H64" s="12" t="inlineStr">
         <is>
@@ -5141,7 +5297,11 @@
           <t>G7384</t>
         </is>
       </c>
-      <c r="F65" s="11" t="n"/>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>149-91-7</t>
+        </is>
+      </c>
       <c r="G65" s="15" t="n"/>
       <c r="H65" s="12" t="inlineStr">
         <is>
@@ -5208,7 +5368,11 @@
           <t>sc-205704</t>
         </is>
       </c>
-      <c r="F66" s="11" t="n"/>
+      <c r="F66" s="11" t="inlineStr">
+        <is>
+          <t>149-91-7</t>
+        </is>
+      </c>
       <c r="G66" s="9" t="n"/>
       <c r="H66" s="12" t="inlineStr">
         <is>
@@ -5413,7 +5577,11 @@
           <t>4840</t>
         </is>
       </c>
-      <c r="F69" s="11" t="n"/>
+      <c r="F69" s="11" t="inlineStr">
+        <is>
+          <t>56-40-6</t>
+        </is>
+      </c>
       <c r="G69" s="15" t="n"/>
       <c r="H69" s="12" t="inlineStr">
         <is>
@@ -5618,7 +5786,11 @@
           <t>C9002</t>
         </is>
       </c>
-      <c r="F72" s="11" t="n"/>
+      <c r="F72" s="11" t="inlineStr">
+        <is>
+          <t>6004-24-6</t>
+        </is>
+      </c>
       <c r="G72" s="9" t="n"/>
       <c r="H72" s="12" t="inlineStr">
         <is>
@@ -5752,7 +5924,11 @@
           <t>H1758</t>
         </is>
       </c>
-      <c r="F74" s="11" t="n"/>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>7647-01-0</t>
+        </is>
+      </c>
       <c r="G74" s="9" t="n"/>
       <c r="H74" s="12" t="inlineStr">
         <is>
@@ -5894,7 +6070,11 @@
           <t>I7378</t>
         </is>
       </c>
-      <c r="F76" s="11" t="n"/>
+      <c r="F76" s="11" t="inlineStr">
+        <is>
+          <t>53-86-1</t>
+        </is>
+      </c>
       <c r="G76" s="9" t="n"/>
       <c r="H76" s="12" t="inlineStr">
         <is>
@@ -6028,7 +6208,11 @@
           <t>5035-4400</t>
         </is>
       </c>
-      <c r="F78" s="11" t="n"/>
+      <c r="F78" s="11" t="inlineStr">
+        <is>
+          <t>67-63-0</t>
+        </is>
+      </c>
       <c r="G78" s="9" t="n"/>
       <c r="H78" s="12" t="inlineStr">
         <is>
@@ -6166,7 +6350,11 @@
           <t>A5960</t>
         </is>
       </c>
-      <c r="F80" s="11" t="n"/>
+      <c r="F80" s="11" t="inlineStr">
+        <is>
+          <t>50-81-7</t>
+        </is>
+      </c>
       <c r="G80" s="9" t="n"/>
       <c r="H80" s="12" t="inlineStr">
         <is>
@@ -6233,7 +6421,11 @@
           <t>168149</t>
         </is>
       </c>
-      <c r="F81" s="11" t="n"/>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>52-90-4</t>
+        </is>
+      </c>
       <c r="G81" s="15" t="n"/>
       <c r="H81" s="12" t="inlineStr">
         <is>
@@ -6300,7 +6492,11 @@
           <t>S4500</t>
         </is>
       </c>
-      <c r="F82" s="11" t="n"/>
+      <c r="F82" s="11" t="inlineStr">
+        <is>
+          <t>56-45-1</t>
+        </is>
+      </c>
       <c r="G82" s="9" t="n"/>
       <c r="H82" s="12" t="inlineStr">
         <is>
@@ -6367,7 +6563,11 @@
           <t>316512</t>
         </is>
       </c>
-      <c r="F83" s="11" t="n"/>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>6080-56-4</t>
+        </is>
+      </c>
       <c r="G83" s="15" t="n"/>
       <c r="H83" s="12" t="inlineStr">
         <is>
@@ -6505,7 +6705,11 @@
           <t>M2670</t>
         </is>
       </c>
-      <c r="F85" s="11" t="n"/>
+      <c r="F85" s="11" t="inlineStr">
+        <is>
+          <t>7791-18-6</t>
+        </is>
+      </c>
       <c r="G85" s="15" t="n"/>
       <c r="H85" s="12" t="inlineStr">
         <is>
@@ -6576,7 +6780,11 @@
           <t>239275</t>
         </is>
       </c>
-      <c r="F86" s="11" t="n"/>
+      <c r="F86" s="11" t="inlineStr">
+        <is>
+          <t>37267-86-0</t>
+        </is>
+      </c>
       <c r="G86" s="9" t="n"/>
       <c r="H86" s="12" t="inlineStr">
         <is>
@@ -6643,7 +6851,11 @@
           <t>A452-4</t>
         </is>
       </c>
-      <c r="F87" s="11" t="n"/>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>67-56-1</t>
+        </is>
+      </c>
       <c r="G87" s="15" t="n"/>
       <c r="H87" s="12" t="inlineStr">
         <is>
@@ -6710,7 +6922,11 @@
           <t>9093-88</t>
         </is>
       </c>
-      <c r="F88" s="11" t="n"/>
+      <c r="F88" s="11" t="inlineStr">
+        <is>
+          <t>67-56-1</t>
+        </is>
+      </c>
       <c r="G88" s="9" t="n"/>
       <c r="H88" s="12" t="inlineStr">
         <is>
@@ -6777,7 +6993,11 @@
           <t>1.06009.1011</t>
         </is>
       </c>
-      <c r="F89" s="11" t="n"/>
+      <c r="F89" s="11" t="inlineStr">
+        <is>
+          <t>67-56-1</t>
+        </is>
+      </c>
       <c r="G89" s="15" t="n"/>
       <c r="H89" s="12" t="inlineStr">
         <is>
@@ -6848,7 +7068,11 @@
           <t>5558-4410</t>
         </is>
       </c>
-      <c r="F90" s="11" t="n"/>
+      <c r="F90" s="11" t="inlineStr">
+        <is>
+          <t>67-56-1</t>
+        </is>
+      </c>
       <c r="G90" s="9" t="n"/>
       <c r="H90" s="12" t="inlineStr">
         <is>
@@ -6915,7 +7139,11 @@
           <t>5558-4410</t>
         </is>
       </c>
-      <c r="F91" s="11" t="n"/>
+      <c r="F91" s="11" t="inlineStr">
+        <is>
+          <t>67-56-1</t>
+        </is>
+      </c>
       <c r="G91" s="15" t="n"/>
       <c r="H91" s="12" t="inlineStr">
         <is>
@@ -6982,7 +7210,11 @@
           <t>856177</t>
         </is>
       </c>
-      <c r="F92" s="11" t="n"/>
+      <c r="F92" s="11" t="inlineStr">
+        <is>
+          <t>1083299-87-9</t>
+        </is>
+      </c>
       <c r="G92" s="9" t="n"/>
       <c r="H92" s="12" t="inlineStr">
         <is>
@@ -7053,7 +7285,11 @@
           <t>N9125</t>
         </is>
       </c>
-      <c r="F93" s="11" t="n"/>
+      <c r="F93" s="11" t="inlineStr">
+        <is>
+          <t>1465-25-4</t>
+        </is>
+      </c>
       <c r="G93" s="15" t="n"/>
       <c r="H93" s="12" t="inlineStr">
         <is>
@@ -7321,7 +7557,11 @@
           <t>PHR1445</t>
         </is>
       </c>
-      <c r="F97" s="11" t="n"/>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>96829-58-2</t>
+        </is>
+      </c>
       <c r="G97" s="15" t="n"/>
       <c r="H97" s="12" t="inlineStr">
         <is>
@@ -7388,7 +7628,11 @@
           <t>C9008</t>
         </is>
       </c>
-      <c r="F98" s="11" t="n"/>
+      <c r="F98" s="11" t="inlineStr">
+        <is>
+          <t>501-98-4</t>
+        </is>
+      </c>
       <c r="G98" s="9" t="n"/>
       <c r="H98" s="12" t="inlineStr">
         <is>
@@ -7455,7 +7699,11 @@
           <t>P0500</t>
         </is>
       </c>
-      <c r="F99" s="11" t="n"/>
+      <c r="F99" s="11" t="inlineStr">
+        <is>
+          <t>57-10-3</t>
+        </is>
+      </c>
       <c r="G99" s="15" t="n"/>
       <c r="H99" s="12" t="inlineStr">
         <is>
@@ -7526,7 +7774,11 @@
           <t>P7626</t>
         </is>
       </c>
-      <c r="F100" s="11" t="n"/>
+      <c r="F100" s="11" t="inlineStr">
+        <is>
+          <t>329-98-6</t>
+        </is>
+      </c>
       <c r="G100" s="9" t="n"/>
       <c r="H100" s="12" t="inlineStr">
         <is>
@@ -7593,7 +7845,11 @@
           <t>345245</t>
         </is>
       </c>
-      <c r="F101" s="11" t="n"/>
+      <c r="F101" s="11" t="inlineStr">
+        <is>
+          <t>7664-38-2</t>
+        </is>
+      </c>
       <c r="G101" s="15" t="n"/>
       <c r="H101" s="12" t="inlineStr">
         <is>
@@ -7794,7 +8050,11 @@
           <t>20598</t>
         </is>
       </c>
-      <c r="F104" s="11" t="n"/>
+      <c r="F104" s="11" t="inlineStr">
+        <is>
+          <t>7447-40-7</t>
+        </is>
+      </c>
       <c r="G104" s="9" t="n"/>
       <c r="H104" s="12" t="inlineStr">
         <is>
@@ -7861,7 +8121,11 @@
           <t>217255</t>
         </is>
       </c>
-      <c r="F105" s="11" t="n"/>
+      <c r="F105" s="11" t="inlineStr">
+        <is>
+          <t>6381-59-5</t>
+        </is>
+      </c>
       <c r="G105" s="15" t="n"/>
       <c r="H105" s="12" t="inlineStr">
         <is>
@@ -7928,7 +8192,11 @@
           <t>p5780</t>
         </is>
       </c>
-      <c r="F106" s="11" t="n"/>
+      <c r="F106" s="11" t="inlineStr">
+        <is>
+          <t>333-93-7</t>
+        </is>
+      </c>
       <c r="G106" s="9" t="n"/>
       <c r="H106" s="12" t="inlineStr">
         <is>
@@ -8058,7 +8326,11 @@
           <t>424455</t>
         </is>
       </c>
-      <c r="F108" s="11" t="n"/>
+      <c r="F108" s="11" t="inlineStr">
+        <is>
+          <t>635-78-9</t>
+        </is>
+      </c>
       <c r="G108" s="9" t="n"/>
       <c r="H108" s="12" t="inlineStr">
         <is>
@@ -8259,7 +8531,11 @@
           <t>17009001</t>
         </is>
       </c>
-      <c r="F111" s="11" t="n"/>
+      <c r="F111" s="11" t="inlineStr">
+        <is>
+          <t>9041-37-6</t>
+        </is>
+      </c>
       <c r="G111" s="15" t="n"/>
       <c r="H111" s="12" t="inlineStr">
         <is>
@@ -8326,7 +8602,11 @@
           <t>D7927</t>
         </is>
       </c>
-      <c r="F112" s="11" t="n"/>
+      <c r="F112" s="11" t="inlineStr">
+        <is>
+          <t>530-59-6</t>
+        </is>
+      </c>
       <c r="G112" s="9" t="n"/>
       <c r="H112" s="12" t="inlineStr">
         <is>
@@ -8393,7 +8673,11 @@
           <t>S7400</t>
         </is>
       </c>
-      <c r="F113" s="11" t="n"/>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>7784-46-5</t>
+        </is>
+      </c>
       <c r="G113" s="15" t="n"/>
       <c r="H113" s="12" t="inlineStr">
         <is>
@@ -8460,7 +8744,11 @@
           <t>S5761</t>
         </is>
       </c>
-      <c r="F114" s="11" t="n"/>
+      <c r="F114" s="11" t="inlineStr">
+        <is>
+          <t>144-55-8</t>
+        </is>
+      </c>
       <c r="G114" s="9" t="n"/>
       <c r="H114" s="12" t="inlineStr">
         <is>
@@ -8527,7 +8815,11 @@
           <t>S6014</t>
         </is>
       </c>
-      <c r="F115" s="11" t="n"/>
+      <c r="F115" s="11" t="inlineStr">
+        <is>
+          <t>144-55-8</t>
+        </is>
+      </c>
       <c r="G115" s="15" t="n"/>
       <c r="H115" s="12" t="inlineStr">
         <is>
@@ -8598,7 +8890,11 @@
           <t>223484</t>
         </is>
       </c>
-      <c r="F116" s="11" t="n"/>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>497-19-8</t>
+        </is>
+      </c>
       <c r="G116" s="9" t="n"/>
       <c r="H116" s="12" t="inlineStr">
         <is>
@@ -8665,7 +8961,11 @@
           <t>222321</t>
         </is>
       </c>
-      <c r="F117" s="11" t="n"/>
+      <c r="F117" s="11" t="inlineStr">
+        <is>
+          <t>497-19-8</t>
+        </is>
+      </c>
       <c r="G117" s="15" t="n"/>
       <c r="H117" s="12" t="inlineStr">
         <is>
@@ -8736,7 +9036,11 @@
           <t>419273</t>
         </is>
       </c>
-      <c r="F118" s="11" t="n"/>
+      <c r="F118" s="11" t="inlineStr">
+        <is>
+          <t>9004-32-4</t>
+        </is>
+      </c>
       <c r="G118" s="9" t="n"/>
       <c r="H118" s="12" t="inlineStr">
         <is>
@@ -8803,7 +9107,11 @@
           <t>419273</t>
         </is>
       </c>
-      <c r="F119" s="11" t="n"/>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>9004-32-4</t>
+        </is>
+      </c>
       <c r="G119" s="15" t="n"/>
       <c r="H119" s="12" t="inlineStr">
         <is>
@@ -8870,7 +9178,11 @@
           <t>4275449</t>
         </is>
       </c>
-      <c r="F120" s="11" t="n"/>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>7647-14-5</t>
+        </is>
+      </c>
       <c r="G120" s="9" t="n"/>
       <c r="H120" s="12" t="inlineStr">
         <is>
@@ -8937,7 +9249,11 @@
           <t>L3771</t>
         </is>
       </c>
-      <c r="F121" s="11" t="n"/>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>151-21-3</t>
+        </is>
+      </c>
       <c r="G121" s="15" t="n"/>
       <c r="H121" s="12" t="inlineStr">
         <is>
@@ -9004,7 +9320,11 @@
           <t>795429</t>
         </is>
       </c>
-      <c r="F122" s="11" t="n"/>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>1310-73-2</t>
+        </is>
+      </c>
       <c r="G122" s="9" t="n"/>
       <c r="H122" s="12" t="inlineStr">
         <is>
@@ -9138,7 +9458,11 @@
           <t>255556</t>
         </is>
       </c>
-      <c r="F124" s="11" t="n"/>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>7681-57-4</t>
+        </is>
+      </c>
       <c r="G124" s="9" t="n"/>
       <c r="H124" s="12" t="inlineStr">
         <is>
@@ -9205,7 +9529,11 @@
           <t>563218</t>
         </is>
       </c>
-      <c r="F125" s="11" t="n"/>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>7632-00-0</t>
+        </is>
+      </c>
       <c r="G125" s="15" t="n"/>
       <c r="H125" s="12" t="inlineStr">
         <is>
@@ -9276,7 +9604,11 @@
           <t>S6508</t>
         </is>
       </c>
-      <c r="F126" s="11" t="n"/>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>13721-39-6</t>
+        </is>
+      </c>
       <c r="G126" s="9" t="n"/>
       <c r="H126" s="12" t="inlineStr">
         <is>
@@ -9343,7 +9675,11 @@
           <t>342483</t>
         </is>
       </c>
-      <c r="F127" s="11" t="n"/>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>7440-23-5</t>
+        </is>
+      </c>
       <c r="G127" s="15" t="n"/>
       <c r="H127" s="12" t="inlineStr">
         <is>
@@ -9410,7 +9746,11 @@
           <t>S3264</t>
         </is>
       </c>
-      <c r="F128" s="11" t="n"/>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>7558-79-4</t>
+        </is>
+      </c>
       <c r="G128" s="9" t="n"/>
       <c r="H128" s="12" t="inlineStr">
         <is>
@@ -9477,7 +9817,11 @@
           <t>S9390</t>
         </is>
       </c>
-      <c r="F129" s="11" t="n"/>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>7782-85-6</t>
+        </is>
+      </c>
       <c r="G129" s="15" t="n"/>
       <c r="H129" s="12" t="inlineStr">
         <is>
@@ -9544,7 +9888,11 @@
           <t>S5261</t>
         </is>
       </c>
-      <c r="F130" s="11" t="n"/>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>10102-18-8</t>
+        </is>
+      </c>
       <c r="G130" s="9" t="n"/>
       <c r="H130" s="12" t="inlineStr">
         <is>
@@ -9611,7 +9959,11 @@
           <t>239321</t>
         </is>
       </c>
-      <c r="F131" s="11" t="n"/>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>7757-83-7</t>
+        </is>
+      </c>
       <c r="G131" s="15" t="n"/>
       <c r="H131" s="12" t="inlineStr">
         <is>
@@ -9678,7 +10030,11 @@
           <t>S4797</t>
         </is>
       </c>
-      <c r="F132" s="11" t="n"/>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>6106-24-7</t>
+        </is>
+      </c>
       <c r="G132" s="9" t="n"/>
       <c r="H132" s="12" t="inlineStr">
         <is>
@@ -9745,7 +10101,11 @@
           <t>47289</t>
         </is>
       </c>
-      <c r="F133" s="11" t="n"/>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>57-50-1</t>
+        </is>
+      </c>
       <c r="G133" s="15" t="n"/>
       <c r="H133" s="12" t="inlineStr">
         <is>
@@ -9804,7 +10164,11 @@
           <t>S9251</t>
         </is>
       </c>
-      <c r="F134" s="11" t="n"/>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>63-74-1</t>
+        </is>
+      </c>
       <c r="G134" s="9" t="n"/>
       <c r="H134" s="12" t="inlineStr">
         <is>
@@ -9871,7 +10235,11 @@
           <t>7683-4100</t>
         </is>
       </c>
-      <c r="F135" s="11" t="n"/>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>7664-93-9</t>
+        </is>
+      </c>
       <c r="G135" s="15" t="n"/>
       <c r="H135" s="12" t="inlineStr">
         <is>
@@ -9946,7 +10314,11 @@
           <t>17919</t>
         </is>
       </c>
-      <c r="F136" s="11" t="n"/>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>110-18-9</t>
+        </is>
+      </c>
       <c r="G136" s="9" t="n"/>
       <c r="H136" s="12" t="inlineStr">
         <is>
@@ -10013,7 +10385,11 @@
           <t>86720</t>
         </is>
       </c>
-      <c r="F137" s="11" t="n"/>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>97-77-8</t>
+        </is>
+      </c>
       <c r="G137" s="15" t="n"/>
       <c r="H137" s="12" t="inlineStr">
         <is>
@@ -10080,7 +10456,11 @@
           <t>C80687</t>
         </is>
       </c>
-      <c r="F138" s="11" t="n"/>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>104-55-2</t>
+        </is>
+      </c>
       <c r="G138" s="9" t="n"/>
       <c r="H138" s="12" t="inlineStr">
         <is>
@@ -10151,7 +10531,11 @@
           <t>133760</t>
         </is>
       </c>
-      <c r="F139" s="11" t="n"/>
+      <c r="F139" s="11" t="inlineStr">
+        <is>
+          <t>621-82-9</t>
+        </is>
+      </c>
       <c r="G139" s="15" t="n"/>
       <c r="H139" s="12" t="inlineStr">
         <is>
@@ -10218,7 +10602,11 @@
           <t>BP152-5</t>
         </is>
       </c>
-      <c r="F140" s="11" t="n"/>
+      <c r="F140" s="11" t="inlineStr">
+        <is>
+          <t>77-86-1</t>
+        </is>
+      </c>
       <c r="G140" s="9" t="n"/>
       <c r="H140" s="12" t="inlineStr">
         <is>
@@ -10620,7 +11008,11 @@
           <t>94770</t>
         </is>
       </c>
-      <c r="F146" s="11" t="n"/>
+      <c r="F146" s="11" t="inlineStr">
+        <is>
+          <t>121-34-6</t>
+        </is>
+      </c>
       <c r="G146" s="9" t="n"/>
       <c r="H146" s="12" t="inlineStr">
         <is>
@@ -11010,7 +11402,11 @@
           <t>SC-203155</t>
         </is>
       </c>
-      <c r="F152" s="11" t="n"/>
+      <c r="F152" s="11" t="inlineStr">
+        <is>
+          <t>480-41-1</t>
+        </is>
+      </c>
       <c r="G152" s="9" t="n"/>
       <c r="H152" s="12" t="inlineStr">
         <is>
@@ -11077,7 +11473,11 @@
           <t>E4143</t>
         </is>
       </c>
-      <c r="F153" s="11" t="n"/>
+      <c r="F153" s="11" t="inlineStr">
+        <is>
+          <t>989-51-5</t>
+        </is>
+      </c>
       <c r="G153" s="15" t="n"/>
       <c r="H153" s="12" t="inlineStr">
         <is>
@@ -11148,7 +11548,11 @@
           <t>sc-205798</t>
         </is>
       </c>
-      <c r="F154" s="11" t="n"/>
+      <c r="F154" s="11" t="inlineStr">
+        <is>
+          <t>18457-55-1</t>
+        </is>
+      </c>
       <c r="G154" s="9" t="n"/>
       <c r="H154" s="12" t="inlineStr">
         <is>
@@ -11223,7 +11627,11 @@
           <t>C1251</t>
         </is>
       </c>
-      <c r="F155" s="11" t="n"/>
+      <c r="F155" s="11" t="inlineStr">
+        <is>
+          <t>88191-48-4</t>
+        </is>
+      </c>
       <c r="G155" s="15" t="n"/>
       <c r="H155" s="12" t="inlineStr">
         <is>
@@ -11294,7 +11702,11 @@
           <t>238813</t>
         </is>
       </c>
-      <c r="F156" s="11" t="n"/>
+      <c r="F156" s="11" t="inlineStr">
+        <is>
+          <t>53188-07-1</t>
+        </is>
+      </c>
       <c r="G156" s="9" t="n"/>
       <c r="H156" s="12" t="inlineStr">
         <is>
@@ -11436,7 +11848,11 @@
           <t>T9889</t>
         </is>
       </c>
-      <c r="F158" s="11" t="n"/>
+      <c r="F158" s="11" t="inlineStr">
+        <is>
+          <t>122-31-6</t>
+        </is>
+      </c>
       <c r="G158" s="9" t="n"/>
       <c r="H158" s="12" t="inlineStr">
         <is>
@@ -11582,7 +11998,11 @@
           <t>D9132; 43180</t>
         </is>
       </c>
-      <c r="F160" s="11" t="n"/>
+      <c r="F160" s="11" t="inlineStr">
+        <is>
+          <t>1898-66-4</t>
+        </is>
+      </c>
       <c r="G160" s="9" t="n"/>
       <c r="H160" s="12" t="inlineStr">
         <is>
@@ -11799,7 +12219,11 @@
           <t>401560250</t>
         </is>
       </c>
-      <c r="F163" s="11" t="n"/>
+      <c r="F163" s="11" t="inlineStr">
+        <is>
+          <t>2997-92-4</t>
+        </is>
+      </c>
       <c r="G163" s="15" t="n"/>
       <c r="H163" s="12" t="inlineStr">
         <is>
@@ -11874,7 +12298,11 @@
           <t>253847</t>
         </is>
       </c>
-      <c r="F164" s="11" t="n"/>
+      <c r="F164" s="11" t="inlineStr">
+        <is>
+          <t>610-02-6</t>
+        </is>
+      </c>
       <c r="G164" s="9" t="n"/>
       <c r="H164" s="12" t="inlineStr">
         <is>
@@ -12024,7 +12452,11 @@
           <t>240141</t>
         </is>
       </c>
-      <c r="F166" s="11" t="n"/>
+      <c r="F166" s="11" t="inlineStr">
+        <is>
+          <t>99-96-7</t>
+        </is>
+      </c>
       <c r="G166" s="9" t="n"/>
       <c r="H166" s="12" t="inlineStr">
         <is>
@@ -12095,7 +12527,11 @@
           <t>65969</t>
         </is>
       </c>
-      <c r="F167" s="11" t="n"/>
+      <c r="F167" s="11" t="inlineStr">
+        <is>
+          <t>87099-73-8</t>
+        </is>
+      </c>
       <c r="G167" s="15" t="n"/>
       <c r="H167" s="12" t="inlineStr">
         <is>
@@ -12166,7 +12602,11 @@
           <t>80427</t>
         </is>
       </c>
-      <c r="F168" s="11" t="n"/>
+      <c r="F168" s="11" t="inlineStr">
+        <is>
+          <t>89886-31-7</t>
+        </is>
+      </c>
       <c r="G168" s="9" t="n"/>
       <c r="H168" s="12" t="inlineStr">
         <is>
@@ -12596,7 +13036,11 @@
           <t>sc-252361</t>
         </is>
       </c>
-      <c r="F174" s="11" t="n"/>
+      <c r="F174" s="11" t="inlineStr">
+        <is>
+          <t>57-06-7</t>
+        </is>
+      </c>
       <c r="G174" s="9" t="n"/>
       <c r="H174" s="12" t="inlineStr">
         <is>
@@ -12671,7 +13115,11 @@
           <t>A35801</t>
         </is>
       </c>
-      <c r="F175" s="11" t="n"/>
+      <c r="F175" s="11" t="inlineStr">
+        <is>
+          <t>592-88-1</t>
+        </is>
+      </c>
       <c r="G175" s="15" t="n"/>
       <c r="H175" s="12" t="inlineStr">
         <is>
@@ -12742,7 +13190,11 @@
           <t>P8765</t>
         </is>
       </c>
-      <c r="F176" s="11" t="n"/>
+      <c r="F176" s="11" t="inlineStr">
+        <is>
+          <t>5108-96-3</t>
+        </is>
+      </c>
       <c r="G176" s="9" t="n"/>
       <c r="H176" s="12" t="inlineStr">
         <is>
@@ -12813,7 +13265,11 @@
           <t>465119</t>
         </is>
       </c>
-      <c r="F177" s="11" t="n"/>
+      <c r="F177" s="11" t="inlineStr">
+        <is>
+          <t>491-67-8</t>
+        </is>
+      </c>
       <c r="G177" s="15" t="n"/>
       <c r="H177" s="12" t="inlineStr">
         <is>
@@ -12888,7 +13344,11 @@
           <t>252492</t>
         </is>
       </c>
-      <c r="F178" s="11" t="n"/>
+      <c r="F178" s="11" t="inlineStr">
+        <is>
+          <t>622-78-6</t>
+        </is>
+      </c>
       <c r="G178" s="9" t="n"/>
       <c r="H178" s="12" t="inlineStr">
         <is>
@@ -12959,7 +13419,11 @@
           <t>CFN98724</t>
         </is>
       </c>
-      <c r="F179" s="11" t="n"/>
+      <c r="F179" s="11" t="inlineStr">
+        <is>
+          <t>477-90-7</t>
+        </is>
+      </c>
       <c r="G179" s="15" t="n"/>
       <c r="H179" s="12" t="inlineStr">
         <is>
@@ -13030,7 +13494,11 @@
           <t>B2629</t>
         </is>
       </c>
-      <c r="F180" s="11" t="n"/>
+      <c r="F180" s="11" t="inlineStr">
+        <is>
+          <t>107-43-7</t>
+        </is>
+      </c>
       <c r="G180" s="9" t="n"/>
       <c r="H180" s="12" t="inlineStr">
         <is>
@@ -13176,7 +13644,11 @@
           <t>C0750</t>
         </is>
       </c>
-      <c r="F182" s="11" t="n"/>
+      <c r="F182" s="11" t="inlineStr">
+        <is>
+          <t>58-08-2</t>
+        </is>
+      </c>
       <c r="G182" s="9" t="n"/>
       <c r="H182" s="12" t="inlineStr">
         <is>
@@ -13247,7 +13719,11 @@
           <t>M2028</t>
         </is>
       </c>
-      <c r="F183" s="11" t="n"/>
+      <c r="F183" s="11" t="inlineStr">
+        <is>
+          <t>404-86-4</t>
+        </is>
+      </c>
       <c r="G183" s="15" t="n"/>
       <c r="H183" s="12" t="inlineStr">
         <is>
@@ -13464,7 +13940,11 @@
           <t>sc-200896</t>
         </is>
       </c>
-      <c r="F186" s="11" t="n"/>
+      <c r="F186" s="11" t="inlineStr">
+        <is>
+          <t>15663-27-1</t>
+        </is>
+      </c>
       <c r="G186" s="9" t="n"/>
       <c r="H186" s="12" t="inlineStr">
         <is>
@@ -13606,7 +14086,11 @@
           <t>CFN98478</t>
         </is>
       </c>
-      <c r="F188" s="11" t="n"/>
+      <c r="F188" s="11" t="inlineStr">
+        <is>
+          <t>35825-57-1</t>
+        </is>
+      </c>
       <c r="G188" s="9" t="n"/>
       <c r="H188" s="12" t="inlineStr">
         <is>
@@ -13677,7 +14161,11 @@
           <t>30024</t>
         </is>
       </c>
-      <c r="F189" s="11" t="n"/>
+      <c r="F189" s="11" t="inlineStr">
+        <is>
+          <t>59865-13-3</t>
+        </is>
+      </c>
       <c r="G189" s="15" t="n"/>
       <c r="H189" s="12" t="inlineStr">
         <is>
@@ -13823,7 +14311,11 @@
           <t>D9542</t>
         </is>
       </c>
-      <c r="F191" s="11" t="n"/>
+      <c r="F191" s="11" t="inlineStr">
+        <is>
+          <t>47165-04-8</t>
+        </is>
+      </c>
       <c r="G191" s="15" t="n"/>
       <c r="H191" s="12" t="inlineStr">
         <is>
@@ -13894,7 +14386,11 @@
           <t>D4902</t>
         </is>
       </c>
-      <c r="F192" s="11" t="n"/>
+      <c r="F192" s="11" t="inlineStr">
+        <is>
+          <t>50-02-2</t>
+        </is>
+      </c>
       <c r="G192" s="9" t="n"/>
       <c r="H192" s="12" t="inlineStr">
         <is>
@@ -13965,7 +14461,11 @@
           <t>sc-227867</t>
         </is>
       </c>
-      <c r="F193" s="11" t="n"/>
+      <c r="F193" s="11" t="inlineStr">
+        <is>
+          <t>119-84-6</t>
+        </is>
+      </c>
       <c r="G193" s="15" t="n"/>
       <c r="H193" s="12" t="inlineStr">
         <is>
@@ -14036,7 +14536,11 @@
           <t>D0632</t>
         </is>
       </c>
-      <c r="F194" s="11" t="n"/>
+      <c r="F194" s="11" t="inlineStr">
+        <is>
+          <t>27565-41-9</t>
+        </is>
+      </c>
       <c r="G194" s="9" t="n"/>
       <c r="H194" s="12" t="inlineStr">
         <is>
@@ -14107,7 +14611,11 @@
           <t>44583</t>
         </is>
       </c>
-      <c r="F195" s="11" t="n"/>
+      <c r="F195" s="11" t="inlineStr">
+        <is>
+          <t>25316-40-9</t>
+        </is>
+      </c>
       <c r="G195" s="15" t="n"/>
       <c r="H195" s="12" t="inlineStr">
         <is>
@@ -14320,7 +14828,11 @@
           <t>E7881, sc-202601</t>
         </is>
       </c>
-      <c r="F198" s="11" t="n"/>
+      <c r="F198" s="11" t="inlineStr">
+        <is>
+          <t>518-82-1</t>
+        </is>
+      </c>
       <c r="G198" s="9" t="n"/>
       <c r="H198" s="12" t="inlineStr">
         <is>
@@ -14387,7 +14899,11 @@
         </is>
       </c>
       <c r="E199" s="15" t="n"/>
-      <c r="F199" s="11" t="n"/>
+      <c r="F199" s="11" t="inlineStr">
+        <is>
+          <t>2002-24-6</t>
+        </is>
+      </c>
       <c r="G199" s="15" t="n"/>
       <c r="H199" s="12" t="inlineStr">
         <is>
@@ -14458,7 +14974,11 @@
           <t>sc-203043</t>
         </is>
       </c>
-      <c r="F200" s="11" t="n"/>
+      <c r="F200" s="11" t="inlineStr">
+        <is>
+          <t>97-53-0</t>
+        </is>
+      </c>
       <c r="G200" s="9" t="n"/>
       <c r="H200" s="12" t="inlineStr">
         <is>
@@ -14529,7 +15049,11 @@
           <t>E3531</t>
         </is>
       </c>
-      <c r="F201" s="11" t="n"/>
+      <c r="F201" s="11" t="inlineStr">
+        <is>
+          <t>518-17-2</t>
+        </is>
+      </c>
       <c r="G201" s="15" t="n"/>
       <c r="H201" s="12" t="inlineStr">
         <is>
@@ -14604,7 +15128,11 @@
           <t>F9037</t>
         </is>
       </c>
-      <c r="F202" s="11" t="n"/>
+      <c r="F202" s="11" t="inlineStr">
+        <is>
+          <t>75-12-7</t>
+        </is>
+      </c>
       <c r="G202" s="9" t="n"/>
       <c r="H202" s="12" t="inlineStr">
         <is>
@@ -14679,7 +15207,11 @@
           <t>A117-50</t>
         </is>
       </c>
-      <c r="F203" s="11" t="n"/>
+      <c r="F203" s="11" t="inlineStr">
+        <is>
+          <t>64-18-6</t>
+        </is>
+      </c>
       <c r="G203" s="15" t="n"/>
       <c r="H203" s="12" t="inlineStr">
         <is>
@@ -14750,7 +15282,11 @@
           <t>282200</t>
         </is>
       </c>
-      <c r="F204" s="11" t="n"/>
+      <c r="F204" s="11" t="inlineStr">
+        <is>
+          <t>548-83-4</t>
+        </is>
+      </c>
       <c r="G204" s="9" t="n"/>
       <c r="H204" s="12" t="inlineStr">
         <is>
@@ -15038,7 +15574,11 @@
           <t>G0885</t>
         </is>
       </c>
-      <c r="F208" s="11" t="n"/>
+      <c r="F208" s="11" t="inlineStr">
+        <is>
+          <t>9005-79-2</t>
+        </is>
+      </c>
       <c r="G208" s="9" t="n"/>
       <c r="H208" s="12" t="inlineStr">
         <is>
@@ -15180,7 +15720,11 @@
           <t>H4125</t>
         </is>
       </c>
-      <c r="F210" s="11" t="n"/>
+      <c r="F210" s="11" t="inlineStr">
+        <is>
+          <t>520-33-2</t>
+        </is>
+      </c>
       <c r="G210" s="9" t="n"/>
       <c r="H210" s="12" t="inlineStr">
         <is>
@@ -15393,7 +15937,11 @@
           <t>I7256</t>
         </is>
       </c>
-      <c r="F213" s="11" t="n"/>
+      <c r="F213" s="11" t="inlineStr">
+        <is>
+          <t>700-06-1</t>
+        </is>
+      </c>
       <c r="G213" s="15" t="n"/>
       <c r="H213" s="12" t="inlineStr">
         <is>
@@ -15464,7 +16012,11 @@
           <t>I10406</t>
         </is>
       </c>
-      <c r="F214" s="11" t="n"/>
+      <c r="F214" s="11" t="inlineStr">
+        <is>
+          <t>146-68-9</t>
+        </is>
+      </c>
       <c r="G214" s="9" t="n"/>
       <c r="H214" s="12" t="inlineStr">
         <is>
@@ -15610,7 +16162,11 @@
           <t>G6133</t>
         </is>
       </c>
-      <c r="F216" s="11" t="n"/>
+      <c r="F216" s="11" t="inlineStr">
+        <is>
+          <t>56-86-0</t>
+        </is>
+      </c>
       <c r="G216" s="9" t="n"/>
       <c r="H216" s="12" t="inlineStr">
         <is>
@@ -15756,7 +16312,11 @@
           <t>G4251</t>
         </is>
       </c>
-      <c r="F218" s="11" t="n"/>
+      <c r="F218" s="11" t="inlineStr">
+        <is>
+          <t>70-18-8</t>
+        </is>
+      </c>
       <c r="G218" s="9" t="n"/>
       <c r="H218" s="12" t="inlineStr">
         <is>
@@ -15898,7 +16458,11 @@
           <t>P9346</t>
         </is>
       </c>
-      <c r="F220" s="11" t="n"/>
+      <c r="F220" s="11" t="inlineStr">
+        <is>
+          <t>108-95-2</t>
+        </is>
+      </c>
       <c r="G220" s="9" t="n"/>
       <c r="H220" s="12" t="inlineStr">
         <is>
@@ -15969,7 +16533,11 @@
           <t>CFN98546</t>
         </is>
       </c>
-      <c r="F221" s="11" t="n"/>
+      <c r="F221" s="11" t="inlineStr">
+        <is>
+          <t>28831-65-4</t>
+        </is>
+      </c>
       <c r="G221" s="15" t="n"/>
       <c r="H221" s="12" t="inlineStr">
         <is>
@@ -16040,7 +16608,11 @@
           <t>M6949</t>
         </is>
       </c>
-      <c r="F222" s="11" t="n"/>
+      <c r="F222" s="11" t="inlineStr">
+        <is>
+          <t>34540-22-2</t>
+        </is>
+      </c>
       <c r="G222" s="9" t="n"/>
       <c r="H222" s="12" t="inlineStr">
         <is>
@@ -16111,7 +16683,11 @@
           <t>40043</t>
         </is>
       </c>
-      <c r="F223" s="11" t="n"/>
+      <c r="F223" s="11" t="inlineStr">
+        <is>
+          <t>580-72-3</t>
+        </is>
+      </c>
       <c r="G223" s="15" t="n"/>
       <c r="H223" s="12" t="inlineStr">
         <is>
@@ -16470,7 +17046,11 @@
           <t>A7250</t>
         </is>
       </c>
-      <c r="F228" s="11" t="n"/>
+      <c r="F228" s="11" t="inlineStr">
+        <is>
+          <t>616-91-1</t>
+        </is>
+      </c>
       <c r="G228" s="9" t="n"/>
       <c r="H228" s="12" t="inlineStr">
         <is>
@@ -16541,7 +17121,11 @@
           <t>94419</t>
         </is>
       </c>
-      <c r="F229" s="11" t="n"/>
+      <c r="F229" s="11" t="inlineStr">
+        <is>
+          <t>906-33-2</t>
+        </is>
+      </c>
       <c r="G229" s="15" t="n"/>
       <c r="H229" s="12" t="inlineStr">
         <is>
@@ -16612,7 +17196,11 @@
           <t>sc-3573A</t>
         </is>
       </c>
-      <c r="F230" s="11" t="n"/>
+      <c r="F230" s="11" t="inlineStr">
+        <is>
+          <t>1405-10-3</t>
+        </is>
+      </c>
       <c r="G230" s="9" t="n"/>
       <c r="H230" s="12" t="inlineStr">
         <is>
@@ -16825,7 +17413,11 @@
           <t>O4578</t>
         </is>
       </c>
-      <c r="F233" s="11" t="n"/>
+      <c r="F233" s="11" t="inlineStr">
+        <is>
+          <t>64224-21-1</t>
+        </is>
+      </c>
       <c r="G233" s="15" t="n"/>
       <c r="H233" s="12" t="inlineStr">
         <is>
@@ -16900,7 +17492,11 @@
           <t>O4139</t>
         </is>
       </c>
-      <c r="F234" s="11" t="n"/>
+      <c r="F234" s="11" t="inlineStr">
+        <is>
+          <t>96829-58-2</t>
+        </is>
+      </c>
       <c r="G234" s="9" t="n"/>
       <c r="H234" s="12" t="inlineStr">
         <is>
@@ -16971,7 +17567,11 @@
           <t>P0500</t>
         </is>
       </c>
-      <c r="F235" s="11" t="n"/>
+      <c r="F235" s="11" t="inlineStr">
+        <is>
+          <t>57-10-3</t>
+        </is>
+      </c>
       <c r="G235" s="15" t="n"/>
       <c r="H235" s="12" t="inlineStr">
         <is>
@@ -17121,7 +17721,11 @@
           <t>253731</t>
         </is>
       </c>
-      <c r="F237" s="11" t="n"/>
+      <c r="F237" s="11" t="inlineStr">
+        <is>
+          <t>2257-09-2</t>
+        </is>
+      </c>
       <c r="G237" s="15" t="n"/>
       <c r="H237" s="12" t="inlineStr">
         <is>
@@ -17267,7 +17871,11 @@
           <t>P5654</t>
         </is>
       </c>
-      <c r="F239" s="11" t="n"/>
+      <c r="F239" s="11" t="inlineStr">
+        <is>
+          <t>36322-90-4</t>
+        </is>
+      </c>
       <c r="G239" s="15" t="n"/>
       <c r="H239" s="12" t="inlineStr">
         <is>
@@ -17409,7 +18017,11 @@
           <t>P4170; 287075</t>
         </is>
       </c>
-      <c r="F241" s="11" t="n"/>
+      <c r="F241" s="11" t="inlineStr">
+        <is>
+          <t>25535-16-4</t>
+        </is>
+      </c>
       <c r="G241" s="15" t="n"/>
       <c r="H241" s="12" t="inlineStr">
         <is>
@@ -18044,7 +18656,11 @@
           <t>S5567</t>
         </is>
       </c>
-      <c r="F250" s="11" t="n"/>
+      <c r="F250" s="11" t="inlineStr">
+        <is>
+          <t>129-56-6</t>
+        </is>
+      </c>
       <c r="G250" s="9" t="n"/>
       <c r="H250" s="12" t="inlineStr">
         <is>
@@ -18407,7 +19023,11 @@
           <t>78666</t>
         </is>
       </c>
-      <c r="F255" s="11" t="n"/>
+      <c r="F255" s="11" t="inlineStr">
+        <is>
+          <t>480-18-2</t>
+        </is>
+      </c>
       <c r="G255" s="15" t="n"/>
       <c r="H255" s="12" t="inlineStr">
         <is>
@@ -18482,7 +19102,11 @@
           <t>T2577</t>
         </is>
       </c>
-      <c r="F256" s="11" t="n"/>
+      <c r="F256" s="11" t="inlineStr">
+        <is>
+          <t>85622-93-1</t>
+        </is>
+      </c>
       <c r="G256" s="9" t="n"/>
       <c r="H256" s="12" t="inlineStr">
         <is>
@@ -18628,7 +19252,11 @@
           <t>42993</t>
         </is>
       </c>
-      <c r="F258" s="11" t="n"/>
+      <c r="F258" s="11" t="inlineStr">
+        <is>
+          <t>83-67-0</t>
+        </is>
+      </c>
       <c r="G258" s="9" t="n"/>
       <c r="H258" s="12" t="inlineStr">
         <is>
@@ -18699,7 +19327,11 @@
           <t>PHR1023</t>
         </is>
       </c>
-      <c r="F259" s="11" t="n"/>
+      <c r="F259" s="11" t="inlineStr">
+        <is>
+          <t>58-55-9</t>
+        </is>
+      </c>
       <c r="G259" s="15" t="n"/>
       <c r="H259" s="12" t="inlineStr">
         <is>
@@ -18770,7 +19402,11 @@
           <t>M2128</t>
         </is>
       </c>
-      <c r="F260" s="11" t="n"/>
+      <c r="F260" s="11" t="inlineStr">
+        <is>
+          <t>298-93-1</t>
+        </is>
+      </c>
       <c r="G260" s="9" t="n"/>
       <c r="H260" s="12" t="inlineStr">
         <is>
@@ -18841,7 +19477,11 @@
           <t>128708</t>
         </is>
       </c>
-      <c r="F261" s="11" t="n"/>
+      <c r="F261" s="11" t="inlineStr">
+        <is>
+          <t>1135-24-6</t>
+        </is>
+      </c>
       <c r="G261" s="15" t="n"/>
       <c r="H261" s="12" t="inlineStr">
         <is>
@@ -18916,7 +19556,11 @@
           <t>648471</t>
         </is>
       </c>
-      <c r="F262" s="11" t="n"/>
+      <c r="F262" s="11" t="inlineStr">
+        <is>
+          <t>53188-07-1</t>
+        </is>
+      </c>
       <c r="G262" s="9" t="n"/>
       <c r="H262" s="12" t="inlineStr">
         <is>
@@ -18987,7 +19631,11 @@
           <t>U6753</t>
         </is>
       </c>
-      <c r="F263" s="11" t="n"/>
+      <c r="F263" s="11" t="inlineStr">
+        <is>
+          <t>77-52-1</t>
+        </is>
+      </c>
       <c r="G263" s="15" t="n"/>
       <c r="H263" s="12" t="inlineStr">
         <is>
@@ -19058,7 +19706,11 @@
           <t>94770</t>
         </is>
       </c>
-      <c r="F264" s="11" t="n"/>
+      <c r="F264" s="11" t="inlineStr">
+        <is>
+          <t>121-34-6</t>
+        </is>
+      </c>
       <c r="G264" s="9" t="n"/>
       <c r="H264" s="12" t="inlineStr">
         <is>
@@ -20344,7 +20996,11 @@
           <t>10010706</t>
         </is>
       </c>
-      <c r="F282" s="11" t="n"/>
+      <c r="F282" s="11" t="inlineStr">
+        <is>
+          <t>522-17-8</t>
+        </is>
+      </c>
       <c r="G282" s="9" t="n"/>
       <c r="H282" s="12" t="inlineStr">
         <is>
@@ -20415,7 +21071,11 @@
           <t>261556</t>
         </is>
       </c>
-      <c r="F283" s="11" t="n"/>
+      <c r="F283" s="11" t="inlineStr">
+        <is>
+          <t>490-83-5</t>
+        </is>
+      </c>
       <c r="G283" s="15" t="n"/>
       <c r="H283" s="12" t="inlineStr">
         <is>
@@ -20486,7 +21146,11 @@
           <t>D1530</t>
         </is>
       </c>
-      <c r="F284" s="11" t="n"/>
+      <c r="F284" s="11" t="inlineStr">
+        <is>
+          <t>32222-06-3</t>
+        </is>
+      </c>
       <c r="G284" s="9" t="n"/>
       <c r="H284" s="12" t="inlineStr">
         <is>
@@ -20557,7 +21221,11 @@
           <t>I5879</t>
         </is>
       </c>
-      <c r="F285" s="11" t="n"/>
+      <c r="F285" s="11" t="inlineStr">
+        <is>
+          <t>28822-58-4</t>
+        </is>
+      </c>
       <c r="G285" s="15" t="n"/>
       <c r="H285" s="12" t="inlineStr">
         <is>
@@ -20628,7 +21296,11 @@
           <t>SC-204624</t>
         </is>
       </c>
-      <c r="F286" s="11" t="n"/>
+      <c r="F286" s="11" t="inlineStr">
+        <is>
+          <t>1968-05-4</t>
+        </is>
+      </c>
       <c r="G286" s="9" t="n"/>
       <c r="H286" s="12" t="inlineStr">
         <is>
@@ -20699,7 +21371,11 @@
           <t>SC-220999</t>
         </is>
       </c>
-      <c r="F287" s="11" t="n"/>
+      <c r="F287" s="11" t="inlineStr">
+        <is>
+          <t>20525-20-6</t>
+        </is>
+      </c>
       <c r="G287" s="15" t="n"/>
       <c r="H287" s="12" t="inlineStr">
         <is>
@@ -20770,7 +21446,11 @@
           <t>R4643</t>
         </is>
       </c>
-      <c r="F288" s="11" t="n"/>
+      <c r="F288" s="11" t="inlineStr">
+        <is>
+          <t>5300-03-8</t>
+        </is>
+      </c>
       <c r="G288" s="9" t="n"/>
       <c r="H288" s="12" t="inlineStr">
         <is>
@@ -20841,7 +21521,11 @@
           <t>A2383</t>
         </is>
       </c>
-      <c r="F289" s="11" t="n"/>
+      <c r="F289" s="11" t="inlineStr">
+        <is>
+          <t>34369-07-8</t>
+        </is>
+      </c>
       <c r="G289" s="15" t="n"/>
       <c r="H289" s="12" t="inlineStr">
         <is>
@@ -21196,7 +21880,11 @@
           <t>SC-201268</t>
         </is>
       </c>
-      <c r="F294" s="11" t="n"/>
+      <c r="F294" s="11" t="inlineStr">
+        <is>
+          <t>136632-32-1</t>
+        </is>
+      </c>
       <c r="G294" s="9" t="n"/>
       <c r="H294" s="12" t="inlineStr">
         <is>
@@ -21267,7 +21955,11 @@
           <t>sc-210812C</t>
         </is>
       </c>
-      <c r="F295" s="11" t="n"/>
+      <c r="F295" s="11" t="inlineStr">
+        <is>
+          <t>69-53-4</t>
+        </is>
+      </c>
       <c r="G295" s="15" t="n"/>
       <c r="H295" s="12" t="inlineStr">
         <is>
@@ -21409,7 +22101,11 @@
           <t>A10132</t>
         </is>
       </c>
-      <c r="F297" s="11" t="n"/>
+      <c r="F297" s="11" t="inlineStr">
+        <is>
+          <t>7659-95-2</t>
+        </is>
+      </c>
       <c r="G297" s="15" t="n"/>
       <c r="H297" s="12" t="inlineStr">
         <is>
@@ -21480,7 +22176,11 @@
           <t>C3100MP</t>
         </is>
       </c>
-      <c r="F298" s="11" t="n"/>
+      <c r="F298" s="11" t="inlineStr">
+        <is>
+          <t>148504-34-1</t>
+        </is>
+      </c>
       <c r="G298" s="9" t="n"/>
       <c r="H298" s="12" t="inlineStr">
         <is>
@@ -21551,7 +22251,11 @@
           <t>70831-56-0</t>
         </is>
       </c>
-      <c r="F299" s="11" t="n"/>
+      <c r="F299" s="11" t="inlineStr">
+        <is>
+          <t>70831-56-0</t>
+        </is>
+      </c>
       <c r="G299" s="15" t="n"/>
       <c r="H299" s="12" t="inlineStr">
         <is>
@@ -21906,7 +22610,11 @@
           <t>C1386</t>
         </is>
       </c>
-      <c r="F304" s="11" t="n"/>
+      <c r="F304" s="11" t="inlineStr">
+        <is>
+          <t>458-37-7</t>
+        </is>
+      </c>
       <c r="G304" s="9" t="n"/>
       <c r="H304" s="12" t="inlineStr">
         <is>
@@ -21977,7 +22685,11 @@
           <t>1494</t>
         </is>
       </c>
-      <c r="F305" s="11" t="n"/>
+      <c r="F305" s="11" t="inlineStr">
+        <is>
+          <t>1428-67-7</t>
+        </is>
+      </c>
       <c r="G305" s="15" t="n"/>
       <c r="H305" s="12" t="inlineStr">
         <is>
@@ -22119,7 +22831,11 @@
           <t>E2250</t>
         </is>
       </c>
-      <c r="F307" s="11" t="n"/>
+      <c r="F307" s="11" t="inlineStr">
+        <is>
+          <t>476-66-4</t>
+        </is>
+      </c>
       <c r="G307" s="15" t="n"/>
       <c r="H307" s="12" t="inlineStr">
         <is>
@@ -22190,7 +22906,11 @@
           <t>F4043</t>
         </is>
       </c>
-      <c r="F308" s="11" t="n"/>
+      <c r="F308" s="11" t="inlineStr">
+        <is>
+          <t>528-48-3</t>
+        </is>
+      </c>
       <c r="G308" s="9" t="n"/>
       <c r="H308" s="12" t="inlineStr">
         <is>
@@ -22261,7 +22981,11 @@
           <t>SC-200891</t>
         </is>
       </c>
-      <c r="F309" s="11" t="n"/>
+      <c r="F309" s="11" t="inlineStr">
+        <is>
+          <t>78824-30-3</t>
+        </is>
+      </c>
       <c r="G309" s="15" t="n"/>
       <c r="H309" s="12" t="inlineStr">
         <is>
@@ -22332,7 +23056,11 @@
           <t>G6649</t>
         </is>
       </c>
-      <c r="F310" s="11" t="n"/>
+      <c r="F310" s="11" t="inlineStr">
+        <is>
+          <t>446-72-0</t>
+        </is>
+      </c>
       <c r="G310" s="9" t="n"/>
       <c r="H310" s="12" t="inlineStr">
         <is>
@@ -22403,7 +23131,11 @@
           <t>2510S</t>
         </is>
       </c>
-      <c r="F311" s="11" t="n"/>
+      <c r="F311" s="11" t="inlineStr">
+        <is>
+          <t>5115-71-9</t>
+        </is>
+      </c>
       <c r="G311" s="15" t="n"/>
       <c r="H311" s="12" t="inlineStr">
         <is>
@@ -22474,7 +23206,11 @@
           <t>2510 S</t>
         </is>
       </c>
-      <c r="F312" s="11" t="n"/>
+      <c r="F312" s="11" t="inlineStr">
+        <is>
+          <t>5115-71-9</t>
+        </is>
+      </c>
       <c r="G312" s="9" t="n"/>
       <c r="H312" s="12" t="inlineStr">
         <is>
@@ -22545,7 +23281,11 @@
           <t>1846926</t>
         </is>
       </c>
-      <c r="F313" s="11" t="n"/>
+      <c r="F313" s="11" t="inlineStr">
+        <is>
+          <t>4091-99-0</t>
+        </is>
+      </c>
       <c r="G313" s="15" t="n"/>
       <c r="H313" s="12" t="inlineStr">
         <is>
@@ -22971,7 +23711,11 @@
           <t>PHR1084-500MG</t>
         </is>
       </c>
-      <c r="F319" s="11" t="n"/>
+      <c r="F319" s="11" t="inlineStr">
+        <is>
+          <t>1115-70-4</t>
+        </is>
+      </c>
       <c r="G319" s="15" t="n"/>
       <c r="H319" s="12" t="inlineStr">
         <is>
@@ -23042,7 +23786,11 @@
           <t>H6025814</t>
         </is>
       </c>
-      <c r="F320" s="11" t="n"/>
+      <c r="F320" s="11" t="inlineStr">
+        <is>
+          <t>443-48-1</t>
+        </is>
+      </c>
       <c r="G320" s="9" t="n"/>
       <c r="H320" s="12" t="inlineStr">
         <is>
@@ -23184,7 +23932,11 @@
           <t>10012600</t>
         </is>
       </c>
-      <c r="F322" s="11" t="n"/>
+      <c r="F322" s="11" t="inlineStr">
+        <is>
+          <t>529-44-2</t>
+        </is>
+      </c>
       <c r="G322" s="9" t="n"/>
       <c r="H322" s="12" t="inlineStr">
         <is>
@@ -23255,7 +24007,11 @@
           <t>sc-3573</t>
         </is>
       </c>
-      <c r="F323" s="11" t="n"/>
+      <c r="F323" s="11" t="inlineStr">
+        <is>
+          <t>1405-10-3</t>
+        </is>
+      </c>
       <c r="G323" s="15" t="n"/>
       <c r="H323" s="12" t="inlineStr">
         <is>
@@ -23326,7 +24082,11 @@
           <t>HY-12222-200mg</t>
         </is>
       </c>
-      <c r="F324" s="11" t="n"/>
+      <c r="F324" s="11" t="inlineStr">
+        <is>
+          <t>459789-99-2</t>
+        </is>
+      </c>
       <c r="G324" s="9" t="n"/>
       <c r="H324" s="12" t="inlineStr">
         <is>
@@ -23397,7 +24157,11 @@
           <t>O1383</t>
         </is>
       </c>
-      <c r="F325" s="11" t="n"/>
+      <c r="F325" s="11" t="inlineStr">
+        <is>
+          <t>112-80-1</t>
+        </is>
+      </c>
       <c r="G325" s="15" t="n"/>
       <c r="H325" s="12" t="inlineStr">
         <is>
@@ -23468,7 +24232,11 @@
           <t>70080</t>
         </is>
       </c>
-      <c r="F326" s="11" t="n"/>
+      <c r="F326" s="11" t="inlineStr">
+        <is>
+          <t>20554-84-1</t>
+        </is>
+      </c>
       <c r="G326" s="9" t="n"/>
       <c r="H326" s="12" t="inlineStr">
         <is>
@@ -23610,7 +24378,11 @@
           <t>P4744</t>
         </is>
       </c>
-      <c r="F328" s="11" t="n"/>
+      <c r="F328" s="11" t="inlineStr">
+        <is>
+          <t>9013-05-2</t>
+        </is>
+      </c>
       <c r="G328" s="9" t="n"/>
       <c r="H328" s="12" t="inlineStr">
         <is>
@@ -23681,7 +24453,11 @@
           <t>P0130-25G</t>
         </is>
       </c>
-      <c r="F329" s="11" t="n"/>
+      <c r="F329" s="11" t="inlineStr">
+        <is>
+          <t>57-83-0</t>
+        </is>
+      </c>
       <c r="G329" s="15" t="n"/>
       <c r="H329" s="12" t="inlineStr">
         <is>
@@ -24040,7 +24816,11 @@
           <t>R4875</t>
         </is>
       </c>
-      <c r="F334" s="11" t="n"/>
+      <c r="F334" s="11" t="inlineStr">
+        <is>
+          <t>108333-82-0</t>
+        </is>
+      </c>
       <c r="G334" s="9" t="n"/>
       <c r="H334" s="12" t="inlineStr">
         <is>
@@ -24182,7 +24962,11 @@
           <t>S0292-10G</t>
         </is>
       </c>
-      <c r="F336" s="11" t="n"/>
+      <c r="F336" s="11" t="inlineStr">
+        <is>
+          <t>65666-07-1</t>
+        </is>
+      </c>
       <c r="G336" s="9" t="n"/>
       <c r="H336" s="12" t="inlineStr">
         <is>
@@ -24253,7 +25037,11 @@
           <t>S9626</t>
         </is>
       </c>
-      <c r="F337" s="11" t="n"/>
+      <c r="F337" s="11" t="inlineStr">
+        <is>
+          <t>15681-89-7</t>
+        </is>
+      </c>
       <c r="G337" s="15" t="n"/>
       <c r="H337" s="12" t="inlineStr">
         <is>
@@ -24537,7 +25325,11 @@
           <t>CFS201801</t>
         </is>
       </c>
-      <c r="F341" s="11" t="n"/>
+      <c r="F341" s="11" t="inlineStr">
+        <is>
+          <t>131651-37-1</t>
+        </is>
+      </c>
       <c r="G341" s="15" t="n"/>
       <c r="H341" s="12" t="inlineStr">
         <is>
@@ -24679,7 +25471,11 @@
           <t>J62790</t>
         </is>
       </c>
-      <c r="F343" s="11" t="n"/>
+      <c r="F343" s="11" t="inlineStr">
+        <is>
+          <t>1404-93-9</t>
+        </is>
+      </c>
       <c r="G343" s="15" t="n"/>
       <c r="H343" s="12" t="inlineStr">
         <is>
@@ -24750,7 +25546,11 @@
           <t>C2211</t>
         </is>
       </c>
-      <c r="F344" s="11" t="n"/>
+      <c r="F344" s="11" t="inlineStr">
+        <is>
+          <t>133407-82-6</t>
+        </is>
+      </c>
       <c r="G344" s="9" t="n"/>
       <c r="H344" s="12" t="inlineStr">
         <is>

--- a/source/Inventory_Master_V7.xlsx
+++ b/source/Inventory_Master_V7.xlsx
@@ -2048,12 +2048,12 @@
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>CHM-0018</t>
+          <t>PRD-0001</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -2675,12 +2675,12 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
-          <t>CHM-0027</t>
+          <t>PRD-0002</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -6611,12 +6611,12 @@
     <row r="84" ht="16" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
         <is>
-          <t>CHM-0083</t>
+          <t>PRD-0003</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -8240,12 +8240,12 @@
     <row r="107" ht="16" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>CHM-0106</t>
+          <t>PRD-0004</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
@@ -11253,12 +11253,12 @@
     <row r="150" ht="16" customHeight="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>CHM-0149</t>
+          <t>PRD-0005</t>
         </is>
       </c>
       <c r="C150" s="9" t="inlineStr">
@@ -11312,12 +11312,12 @@
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>CHM-0150</t>
+          <t>PRD-0006</t>
         </is>
       </c>
       <c r="C151" s="15" t="inlineStr">
@@ -11900,12 +11900,12 @@
     <row r="159" ht="16" customHeight="1">
       <c r="A159" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B159" s="16" t="inlineStr">
         <is>
-          <t>CHM-0158</t>
+          <t>PRD-0007</t>
         </is>
       </c>
       <c r="C159" s="15" t="inlineStr">
@@ -15843,12 +15843,12 @@
     <row r="212" ht="16" customHeight="1">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>CHM-0211</t>
+          <t>PRD-0008</t>
         </is>
       </c>
       <c r="C212" s="9" t="inlineStr">
@@ -16364,12 +16364,12 @@
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B219" s="16" t="inlineStr">
         <is>
-          <t>CHM-0218</t>
+          <t>PRD-0009</t>
         </is>
       </c>
       <c r="C219" s="15" t="inlineStr">
@@ -19979,12 +19979,12 @@
     <row r="268" ht="16" customHeight="1">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B268" s="10" t="inlineStr">
         <is>
-          <t>CHM-0267</t>
+          <t>PRD-0010</t>
         </is>
       </c>
       <c r="C268" s="9" t="inlineStr">
@@ -20050,12 +20050,12 @@
     <row r="269" ht="16" customHeight="1">
       <c r="A269" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B269" s="16" t="inlineStr">
         <is>
-          <t>CHM-0268</t>
+          <t>PRD-0011</t>
         </is>
       </c>
       <c r="C269" s="15" t="inlineStr">
@@ -20121,12 +20121,12 @@
     <row r="270" ht="16" customHeight="1">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B270" s="10" t="inlineStr">
         <is>
-          <t>CHM-0269</t>
+          <t>PRD-0012</t>
         </is>
       </c>
       <c r="C270" s="9" t="inlineStr">
@@ -20192,12 +20192,12 @@
     <row r="271" ht="16" customHeight="1">
       <c r="A271" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B271" s="16" t="inlineStr">
         <is>
-          <t>CHM-0270</t>
+          <t>PRD-0013</t>
         </is>
       </c>
       <c r="C271" s="15" t="inlineStr">
@@ -20263,12 +20263,12 @@
     <row r="272" ht="16" customHeight="1">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B272" s="10" t="inlineStr">
         <is>
-          <t>CHM-0271</t>
+          <t>PRD-0014</t>
         </is>
       </c>
       <c r="C272" s="9" t="inlineStr">
@@ -20334,12 +20334,12 @@
     <row r="273" ht="16" customHeight="1">
       <c r="A273" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B273" s="16" t="inlineStr">
         <is>
-          <t>CHM-0272</t>
+          <t>PRD-0015</t>
         </is>
       </c>
       <c r="C273" s="15" t="inlineStr">
@@ -20405,12 +20405,12 @@
     <row r="274" ht="16" customHeight="1">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B274" s="10" t="inlineStr">
         <is>
-          <t>CHM-0273</t>
+          <t>PRD-0016</t>
         </is>
       </c>
       <c r="C274" s="9" t="inlineStr">
@@ -20476,12 +20476,12 @@
     <row r="275" ht="16" customHeight="1">
       <c r="A275" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B275" s="16" t="inlineStr">
         <is>
-          <t>CHM-0274</t>
+          <t>PRD-0017</t>
         </is>
       </c>
       <c r="C275" s="15" t="inlineStr">
@@ -20547,12 +20547,12 @@
     <row r="276" ht="16" customHeight="1">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B276" s="10" t="inlineStr">
         <is>
-          <t>CHM-0275</t>
+          <t>PRD-0018</t>
         </is>
       </c>
       <c r="C276" s="9" t="inlineStr">
@@ -20618,12 +20618,12 @@
     <row r="277" ht="16" customHeight="1">
       <c r="A277" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B277" s="16" t="inlineStr">
         <is>
-          <t>CHM-0276</t>
+          <t>PRD-0019</t>
         </is>
       </c>
       <c r="C277" s="15" t="inlineStr">
@@ -20689,12 +20689,12 @@
     <row r="278" ht="16" customHeight="1">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B278" s="10" t="inlineStr">
         <is>
-          <t>CHM-0277</t>
+          <t>PRD-0020</t>
         </is>
       </c>
       <c r="C278" s="9" t="inlineStr">
@@ -20760,12 +20760,12 @@
     <row r="279" ht="16" customHeight="1">
       <c r="A279" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B279" s="16" t="inlineStr">
         <is>
-          <t>CHM-0278</t>
+          <t>PRD-0021</t>
         </is>
       </c>
       <c r="C279" s="15" t="inlineStr">
@@ -20831,12 +20831,12 @@
     <row r="280" ht="16" customHeight="1">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B280" s="10" t="inlineStr">
         <is>
-          <t>CHM-0279</t>
+          <t>PRD-0022</t>
         </is>
       </c>
       <c r="C280" s="9" t="inlineStr">
@@ -20902,12 +20902,12 @@
     <row r="281" ht="16" customHeight="1">
       <c r="A281" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B281" s="16" t="inlineStr">
         <is>
-          <t>CHM-0280</t>
+          <t>PRD-0023</t>
         </is>
       </c>
       <c r="C281" s="15" t="inlineStr">
@@ -21573,12 +21573,12 @@
     <row r="290" ht="16" customHeight="1">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B290" s="10" t="inlineStr">
         <is>
-          <t>CHM-0289</t>
+          <t>PRD-0024</t>
         </is>
       </c>
       <c r="C290" s="9" t="inlineStr">
@@ -21644,12 +21644,12 @@
     <row r="291" ht="16" customHeight="1">
       <c r="A291" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B291" s="16" t="inlineStr">
         <is>
-          <t>CHM-0290</t>
+          <t>PRD-0025</t>
         </is>
       </c>
       <c r="C291" s="15" t="inlineStr">
@@ -21715,12 +21715,12 @@
     <row r="292" ht="16" customHeight="1">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B292" s="10" t="inlineStr">
         <is>
-          <t>CHM-0291</t>
+          <t>PRD-0026</t>
         </is>
       </c>
       <c r="C292" s="9" t="inlineStr">
@@ -21786,12 +21786,12 @@
     <row r="293" ht="16" customHeight="1">
       <c r="A293" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B293" s="16" t="inlineStr">
         <is>
-          <t>CHM-0292</t>
+          <t>PRD-0027</t>
         </is>
       </c>
       <c r="C293" s="15" t="inlineStr">
@@ -22374,12 +22374,12 @@
     <row r="301" ht="16" customHeight="1">
       <c r="A301" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B301" s="16" t="inlineStr">
         <is>
-          <t>CHM-0300</t>
+          <t>PRD-0028</t>
         </is>
       </c>
       <c r="C301" s="15" t="inlineStr">
@@ -22445,12 +22445,12 @@
     <row r="302" ht="16" customHeight="1">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B302" s="10" t="inlineStr">
         <is>
-          <t>CHM-0301</t>
+          <t>PRD-0029</t>
         </is>
       </c>
       <c r="C302" s="9" t="inlineStr">
@@ -22737,12 +22737,12 @@
     <row r="306" ht="16" customHeight="1">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B306" s="10" t="inlineStr">
         <is>
-          <t>CHM-0305</t>
+          <t>PRD-0030</t>
         </is>
       </c>
       <c r="C306" s="9" t="inlineStr">
@@ -23333,12 +23333,12 @@
     <row r="314" ht="16" customHeight="1">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B314" s="10" t="inlineStr">
         <is>
-          <t>CHM-0313</t>
+          <t>PRD-0031</t>
         </is>
       </c>
       <c r="C314" s="9" t="inlineStr">
@@ -23404,12 +23404,12 @@
     <row r="315" ht="16" customHeight="1">
       <c r="A315" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B315" s="16" t="inlineStr">
         <is>
-          <t>CHM-0314</t>
+          <t>PRD-0032</t>
         </is>
       </c>
       <c r="C315" s="15" t="inlineStr">
@@ -23475,12 +23475,12 @@
     <row r="316" ht="16" customHeight="1">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B316" s="10" t="inlineStr">
         <is>
-          <t>CHM-0315</t>
+          <t>PRD-0033</t>
         </is>
       </c>
       <c r="C316" s="9" t="inlineStr">
@@ -23546,12 +23546,12 @@
     <row r="317" ht="16" customHeight="1">
       <c r="A317" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B317" s="16" t="inlineStr">
         <is>
-          <t>CHM-0316</t>
+          <t>PRD-0034</t>
         </is>
       </c>
       <c r="C317" s="15" t="inlineStr">
@@ -23838,12 +23838,12 @@
     <row r="321" ht="16" customHeight="1">
       <c r="A321" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B321" s="16" t="inlineStr">
         <is>
-          <t>CHM-0320</t>
+          <t>PRD-0035</t>
         </is>
       </c>
       <c r="C321" s="15" t="inlineStr">
@@ -24284,12 +24284,12 @@
     <row r="327" ht="16" customHeight="1">
       <c r="A327" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B327" s="16" t="inlineStr">
         <is>
-          <t>CHM-0326</t>
+          <t>PRD-0036</t>
         </is>
       </c>
       <c r="C327" s="15" t="inlineStr">
@@ -24505,12 +24505,12 @@
     <row r="330" ht="16" customHeight="1">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B330" s="10" t="inlineStr">
         <is>
-          <t>CHM-0329</t>
+          <t>PRD-0037</t>
         </is>
       </c>
       <c r="C330" s="9" t="inlineStr">
@@ -24722,12 +24722,12 @@
     <row r="333" ht="16" customHeight="1">
       <c r="A333" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B333" s="16" t="inlineStr">
         <is>
-          <t>CHM-0332</t>
+          <t>PRD-0038</t>
         </is>
       </c>
       <c r="C333" s="15" t="inlineStr">
@@ -24868,12 +24868,12 @@
     <row r="335" ht="16" customHeight="1">
       <c r="A335" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B335" s="16" t="inlineStr">
         <is>
-          <t>CHM-0334</t>
+          <t>PRD-0039</t>
         </is>
       </c>
       <c r="C335" s="15" t="inlineStr">
@@ -25089,12 +25089,12 @@
     <row r="338" ht="16" customHeight="1">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B338" s="10" t="inlineStr">
         <is>
-          <t>CHM-0337</t>
+          <t>PRD-0040</t>
         </is>
       </c>
       <c r="C338" s="9" t="inlineStr">
@@ -25160,12 +25160,12 @@
     <row r="339" ht="16" customHeight="1">
       <c r="A339" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B339" s="16" t="inlineStr">
         <is>
-          <t>CHM-0338</t>
+          <t>PRD-0041</t>
         </is>
       </c>
       <c r="C339" s="15" t="inlineStr">
@@ -25231,12 +25231,12 @@
     <row r="340" ht="16" customHeight="1">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B340" s="10" t="inlineStr">
         <is>
-          <t>CHM-0339</t>
+          <t>PRD-0042</t>
         </is>
       </c>
       <c r="C340" s="9" t="inlineStr">
@@ -25377,12 +25377,12 @@
     <row r="342" ht="16" customHeight="1">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B342" s="10" t="inlineStr">
         <is>
-          <t>CHM-0341</t>
+          <t>PRD-0043</t>
         </is>
       </c>
       <c r="C342" s="9" t="inlineStr">
@@ -25811,12 +25811,12 @@
     <row r="348" ht="16" customHeight="1">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B348" s="10" t="inlineStr">
         <is>
-          <t>CHM-0347</t>
+          <t>PRD-0044</t>
         </is>
       </c>
       <c r="C348" s="9" t="inlineStr">
@@ -25882,12 +25882,12 @@
     <row r="349" ht="16" customHeight="1">
       <c r="A349" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B349" s="16" t="inlineStr">
         <is>
-          <t>CHM-0348</t>
+          <t>PRD-0045</t>
         </is>
       </c>
       <c r="C349" s="15" t="inlineStr">
@@ -25953,12 +25953,12 @@
     <row r="350" ht="16" customHeight="1">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B350" s="10" t="inlineStr">
         <is>
-          <t>CHM-0349</t>
+          <t>PRD-0046</t>
         </is>
       </c>
       <c r="C350" s="9" t="inlineStr">
@@ -26024,12 +26024,12 @@
     <row r="351" ht="16" customHeight="1">
       <c r="A351" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B351" s="16" t="inlineStr">
         <is>
-          <t>CHM-0350</t>
+          <t>PRD-0047</t>
         </is>
       </c>
       <c r="C351" s="15" t="inlineStr">
@@ -26095,12 +26095,12 @@
     <row r="352" ht="16" customHeight="1">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B352" s="10" t="inlineStr">
         <is>
-          <t>CHM-0351</t>
+          <t>PRD-0048</t>
         </is>
       </c>
       <c r="C352" s="9" t="inlineStr">
@@ -49277,12 +49277,12 @@
     <row r="678" ht="16" customHeight="1">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B678" s="10" t="inlineStr">
         <is>
-          <t>PRD-0001</t>
+          <t>PRD-0049</t>
         </is>
       </c>
       <c r="C678" s="9" t="inlineStr">
@@ -49340,12 +49340,12 @@
     <row r="679" ht="16" customHeight="1">
       <c r="A679" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B679" s="16" t="inlineStr">
         <is>
-          <t>PRD-0002</t>
+          <t>PRD-0050</t>
         </is>
       </c>
       <c r="C679" s="15" t="inlineStr">
@@ -49403,12 +49403,12 @@
     <row r="680" ht="16" customHeight="1">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B680" s="10" t="inlineStr">
         <is>
-          <t>PRD-0003</t>
+          <t>PRD-0051</t>
         </is>
       </c>
       <c r="C680" s="9" t="inlineStr">
@@ -49466,12 +49466,12 @@
     <row r="681" ht="16" customHeight="1">
       <c r="A681" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B681" s="16" t="inlineStr">
         <is>
-          <t>PRD-0004</t>
+          <t>PRD-0052</t>
         </is>
       </c>
       <c r="C681" s="15" t="inlineStr">
@@ -49600,12 +49600,12 @@
     <row r="683" ht="16" customHeight="1">
       <c r="A683" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B683" s="16" t="inlineStr">
         <is>
-          <t>PRD-0006</t>
+          <t>PRD-0053</t>
         </is>
       </c>
       <c r="C683" s="15" t="inlineStr">
@@ -49789,12 +49789,12 @@
     <row r="686" ht="16" customHeight="1">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B686" s="10" t="inlineStr">
         <is>
-          <t>PRD-0009</t>
+          <t>PRD-0054</t>
         </is>
       </c>
       <c r="C686" s="9" t="inlineStr">
@@ -49852,12 +49852,12 @@
     <row r="687" ht="16" customHeight="1">
       <c r="A687" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B687" s="16" t="inlineStr">
         <is>
-          <t>PRD-0010</t>
+          <t>PRD-0055</t>
         </is>
       </c>
       <c r="C687" s="15" t="inlineStr">
@@ -49915,12 +49915,12 @@
     <row r="688" ht="16" customHeight="1">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B688" s="10" t="inlineStr">
         <is>
-          <t>PRD-0011</t>
+          <t>PRD-0056</t>
         </is>
       </c>
       <c r="C688" s="9" t="inlineStr">
@@ -49978,12 +49978,12 @@
     <row r="689" ht="16" customHeight="1">
       <c r="A689" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B689" s="16" t="inlineStr">
         <is>
-          <t>PRD-0012</t>
+          <t>PRD-0057</t>
         </is>
       </c>
       <c r="C689" s="15" t="inlineStr">
@@ -50041,12 +50041,12 @@
     <row r="690" ht="16" customHeight="1">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B690" s="10" t="inlineStr">
         <is>
-          <t>PRD-0013</t>
+          <t>PRD-0058</t>
         </is>
       </c>
       <c r="C690" s="9" t="inlineStr">
@@ -50104,12 +50104,12 @@
     <row r="691" ht="16" customHeight="1">
       <c r="A691" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B691" s="16" t="inlineStr">
         <is>
-          <t>PRD-0014</t>
+          <t>PRD-0059</t>
         </is>
       </c>
       <c r="C691" s="15" t="inlineStr">
@@ -50167,12 +50167,12 @@
     <row r="692" ht="16" customHeight="1">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B692" s="10" t="inlineStr">
         <is>
-          <t>PRD-0015</t>
+          <t>PRD-0060</t>
         </is>
       </c>
       <c r="C692" s="9" t="inlineStr">
@@ -50423,12 +50423,12 @@
     <row r="696" ht="16" customHeight="1">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B696" s="10" t="inlineStr">
         <is>
-          <t>PRD-0019</t>
+          <t>PRD-0061</t>
         </is>
       </c>
       <c r="C696" s="9" t="inlineStr">
@@ -50486,12 +50486,12 @@
     <row r="697" ht="16" customHeight="1">
       <c r="A697" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B697" s="16" t="inlineStr">
         <is>
-          <t>PRD-0020</t>
+          <t>PRD-0062</t>
         </is>
       </c>
       <c r="C697" s="15" t="inlineStr">
@@ -50549,12 +50549,12 @@
     <row r="698" ht="16" customHeight="1">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B698" s="10" t="inlineStr">
         <is>
-          <t>PRD-0021</t>
+          <t>PRD-0063</t>
         </is>
       </c>
       <c r="C698" s="9" t="inlineStr">
@@ -50612,12 +50612,12 @@
     <row r="699" ht="16" customHeight="1">
       <c r="A699" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B699" s="16" t="inlineStr">
         <is>
-          <t>PRD-0022</t>
+          <t>PRD-0064</t>
         </is>
       </c>
       <c r="C699" s="15" t="inlineStr">
@@ -50675,12 +50675,12 @@
     <row r="700" ht="16" customHeight="1">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B700" s="10" t="inlineStr">
         <is>
-          <t>PRD-0023</t>
+          <t>PRD-0065</t>
         </is>
       </c>
       <c r="C700" s="9" t="inlineStr">
@@ -50738,12 +50738,12 @@
     <row r="701" ht="16" customHeight="1">
       <c r="A701" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B701" s="16" t="inlineStr">
         <is>
-          <t>PRD-0024</t>
+          <t>PRD-0066</t>
         </is>
       </c>
       <c r="C701" s="15" t="inlineStr">
@@ -50864,12 +50864,12 @@
     <row r="703" ht="16" customHeight="1">
       <c r="A703" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B703" s="16" t="inlineStr">
         <is>
-          <t>PRD-0026</t>
+          <t>PRD-0067</t>
         </is>
       </c>
       <c r="C703" s="15" t="inlineStr">
@@ -50927,12 +50927,12 @@
     <row r="704" ht="16" customHeight="1">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B704" s="10" t="inlineStr">
         <is>
-          <t>PRD-0027</t>
+          <t>PRD-0068</t>
         </is>
       </c>
       <c r="C704" s="9" t="inlineStr">
@@ -50990,12 +50990,12 @@
     <row r="705" ht="16" customHeight="1">
       <c r="A705" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B705" s="16" t="inlineStr">
         <is>
-          <t>PRD-0028</t>
+          <t>PRD-0069</t>
         </is>
       </c>
       <c r="C705" s="15" t="inlineStr">
@@ -51053,12 +51053,12 @@
     <row r="706" ht="16" customHeight="1">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B706" s="10" t="inlineStr">
         <is>
-          <t>PRD-0029</t>
+          <t>PRD-0070</t>
         </is>
       </c>
       <c r="C706" s="9" t="inlineStr">
@@ -51112,12 +51112,12 @@
     <row r="707" ht="16" customHeight="1">
       <c r="A707" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B707" s="16" t="inlineStr">
         <is>
-          <t>PRD-0030</t>
+          <t>PRD-0071</t>
         </is>
       </c>
       <c r="C707" s="15" t="inlineStr">
@@ -51376,12 +51376,12 @@
     <row r="711" ht="16" customHeight="1">
       <c r="A711" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B711" s="16" t="inlineStr">
         <is>
-          <t>PRD-0034</t>
+          <t>PRD-0072</t>
         </is>
       </c>
       <c r="C711" s="15" t="inlineStr">
@@ -51439,12 +51439,12 @@
     <row r="712" ht="16" customHeight="1">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B712" s="10" t="inlineStr">
         <is>
-          <t>PRD-0035</t>
+          <t>PRD-0073</t>
         </is>
       </c>
       <c r="C712" s="9" t="inlineStr">
@@ -51502,12 +51502,12 @@
     <row r="713" ht="16" customHeight="1">
       <c r="A713" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B713" s="16" t="inlineStr">
         <is>
-          <t>PRD-0036</t>
+          <t>PRD-0074</t>
         </is>
       </c>
       <c r="C713" s="15" t="inlineStr">
@@ -51565,12 +51565,12 @@
     <row r="714" ht="16" customHeight="1">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B714" s="10" t="inlineStr">
         <is>
-          <t>PRD-0037</t>
+          <t>PRD-0075</t>
         </is>
       </c>
       <c r="C714" s="9" t="inlineStr">
@@ -51628,12 +51628,12 @@
     <row r="715" ht="16" customHeight="1">
       <c r="A715" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B715" s="16" t="inlineStr">
         <is>
-          <t>PRD-0038</t>
+          <t>PRD-0076</t>
         </is>
       </c>
       <c r="C715" s="15" t="inlineStr">
@@ -51691,12 +51691,12 @@
     <row r="716" ht="16" customHeight="1">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B716" s="10" t="inlineStr">
         <is>
-          <t>PRD-0039</t>
+          <t>PRD-0077</t>
         </is>
       </c>
       <c r="C716" s="9" t="inlineStr">
@@ -51754,12 +51754,12 @@
     <row r="717" ht="16" customHeight="1">
       <c r="A717" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B717" s="16" t="inlineStr">
         <is>
-          <t>PRD-0040</t>
+          <t>PRD-0078</t>
         </is>
       </c>
       <c r="C717" s="15" t="inlineStr">
@@ -51817,12 +51817,12 @@
     <row r="718" ht="16" customHeight="1">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B718" s="10" t="inlineStr">
         <is>
-          <t>PRD-0041</t>
+          <t>PRD-0079</t>
         </is>
       </c>
       <c r="C718" s="9" t="inlineStr">
@@ -52483,12 +52483,12 @@
     <row r="728" ht="16" customHeight="1">
       <c r="A728" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B728" s="10" t="inlineStr">
         <is>
-          <t>PRD-0051</t>
+          <t>PRD-0080</t>
         </is>
       </c>
       <c r="C728" s="9" t="inlineStr">
@@ -52546,12 +52546,12 @@
     <row r="729" ht="16" customHeight="1">
       <c r="A729" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B729" s="16" t="inlineStr">
         <is>
-          <t>PRD-0052</t>
+          <t>PRD-0081</t>
         </is>
       </c>
       <c r="C729" s="15" t="inlineStr">
@@ -52609,12 +52609,12 @@
     <row r="730" ht="16" customHeight="1">
       <c r="A730" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B730" s="10" t="inlineStr">
         <is>
-          <t>PRD-0053</t>
+          <t>PRD-0082</t>
         </is>
       </c>
       <c r="C730" s="9" t="inlineStr">
@@ -52672,12 +52672,12 @@
     <row r="731" ht="16" customHeight="1">
       <c r="A731" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B731" s="16" t="inlineStr">
         <is>
-          <t>PRD-0054</t>
+          <t>PRD-0083</t>
         </is>
       </c>
       <c r="C731" s="15" t="inlineStr">
@@ -52735,12 +52735,12 @@
     <row r="732" ht="16" customHeight="1">
       <c r="A732" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B732" s="10" t="inlineStr">
         <is>
-          <t>PRD-0055</t>
+          <t>PRD-0084</t>
         </is>
       </c>
       <c r="C732" s="9" t="inlineStr">
@@ -52798,12 +52798,12 @@
     <row r="733" ht="16" customHeight="1">
       <c r="A733" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B733" s="16" t="inlineStr">
         <is>
-          <t>PRD-0056</t>
+          <t>PRD-0085</t>
         </is>
       </c>
       <c r="C733" s="15" t="inlineStr">
@@ -52861,12 +52861,12 @@
     <row r="734" ht="16" customHeight="1">
       <c r="A734" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B734" s="10" t="inlineStr">
         <is>
-          <t>PRD-0057</t>
+          <t>PRD-0086</t>
         </is>
       </c>
       <c r="C734" s="9" t="inlineStr">
@@ -52924,12 +52924,12 @@
     <row r="735" ht="16" customHeight="1">
       <c r="A735" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B735" s="16" t="inlineStr">
         <is>
-          <t>PRD-0058</t>
+          <t>PRD-0087</t>
         </is>
       </c>
       <c r="C735" s="15" t="inlineStr">
@@ -52987,12 +52987,12 @@
     <row r="736" ht="16" customHeight="1">
       <c r="A736" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B736" s="10" t="inlineStr">
         <is>
-          <t>PRD-0059</t>
+          <t>PRD-0088</t>
         </is>
       </c>
       <c r="C736" s="9" t="inlineStr">
@@ -53050,12 +53050,12 @@
     <row r="737" ht="16" customHeight="1">
       <c r="A737" s="15" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B737" s="16" t="inlineStr">
         <is>
-          <t>PRD-0060</t>
+          <t>PRD-0089</t>
         </is>
       </c>
       <c r="C737" s="15" t="inlineStr">
@@ -53113,12 +53113,12 @@
     <row r="738" ht="16" customHeight="1">
       <c r="A738" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B738" s="10" t="inlineStr">
         <is>
-          <t>PRD-0061</t>
+          <t>PRD-0090</t>
         </is>
       </c>
       <c r="C738" s="9" t="inlineStr">
@@ -53176,12 +53176,12 @@
     <row r="739" ht="16" customHeight="1">
       <c r="A739" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B739" s="16" t="inlineStr">
         <is>
-          <t>PRD-0062</t>
+          <t>PRD-0091</t>
         </is>
       </c>
       <c r="C739" s="15" t="inlineStr">
@@ -53239,12 +53239,12 @@
     <row r="740" ht="16" customHeight="1">
       <c r="A740" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B740" s="10" t="inlineStr">
         <is>
-          <t>PRD-0063</t>
+          <t>PRD-0092</t>
         </is>
       </c>
       <c r="C740" s="9" t="inlineStr">
@@ -53302,12 +53302,12 @@
     <row r="741" ht="16" customHeight="1">
       <c r="A741" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B741" s="16" t="inlineStr">
         <is>
-          <t>PRD-0064</t>
+          <t>PRD-0093</t>
         </is>
       </c>
       <c r="C741" s="15" t="inlineStr">
@@ -53361,12 +53361,12 @@
     <row r="742" ht="16" customHeight="1">
       <c r="A742" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B742" s="10" t="inlineStr">
         <is>
-          <t>PRD-0065</t>
+          <t>PRD-0094</t>
         </is>
       </c>
       <c r="C742" s="9" t="inlineStr">
@@ -53420,12 +53420,12 @@
     <row r="743" ht="16" customHeight="1">
       <c r="A743" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B743" s="16" t="inlineStr">
         <is>
-          <t>PRD-0066</t>
+          <t>PRD-0095</t>
         </is>
       </c>
       <c r="C743" s="15" t="inlineStr">
@@ -53483,12 +53483,12 @@
     <row r="744" ht="16" customHeight="1">
       <c r="A744" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B744" s="10" t="inlineStr">
         <is>
-          <t>PRD-0067</t>
+          <t>PRD-0096</t>
         </is>
       </c>
       <c r="C744" s="9" t="inlineStr">
@@ -53546,12 +53546,12 @@
     <row r="745" ht="16" customHeight="1">
       <c r="A745" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B745" s="16" t="inlineStr">
         <is>
-          <t>PRD-0068</t>
+          <t>PRD-0097</t>
         </is>
       </c>
       <c r="C745" s="15" t="inlineStr">
@@ -53609,12 +53609,12 @@
     <row r="746" ht="16" customHeight="1">
       <c r="A746" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B746" s="10" t="inlineStr">
         <is>
-          <t>PRD-0069</t>
+          <t>PRD-0098</t>
         </is>
       </c>
       <c r="C746" s="9" t="inlineStr">
@@ -53672,12 +53672,12 @@
     <row r="747" ht="16" customHeight="1">
       <c r="A747" s="15" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B747" s="16" t="inlineStr">
         <is>
-          <t>PRD-0070</t>
+          <t>PRD-0099</t>
         </is>
       </c>
       <c r="C747" s="15" t="inlineStr">
@@ -53991,12 +53991,12 @@
     <row r="752" ht="16" customHeight="1">
       <c r="A752" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B752" s="10" t="inlineStr">
         <is>
-          <t>PRD-0075</t>
+          <t>PRD-0100</t>
         </is>
       </c>
       <c r="C752" s="9" t="inlineStr">
@@ -54054,12 +54054,12 @@
     <row r="753" ht="16" customHeight="1">
       <c r="A753" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B753" s="16" t="inlineStr">
         <is>
-          <t>PRD-0076</t>
+          <t>PRD-0101</t>
         </is>
       </c>
       <c r="C753" s="15" t="inlineStr">
@@ -54117,12 +54117,12 @@
     <row r="754" ht="16" customHeight="1">
       <c r="A754" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B754" s="10" t="inlineStr">
         <is>
-          <t>PRD-0077</t>
+          <t>PRD-0102</t>
         </is>
       </c>
       <c r="C754" s="9" t="inlineStr">
@@ -54180,12 +54180,12 @@
     <row r="755" ht="16" customHeight="1">
       <c r="A755" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B755" s="16" t="inlineStr">
         <is>
-          <t>PRD-0078</t>
+          <t>PRD-0103</t>
         </is>
       </c>
       <c r="C755" s="15" t="inlineStr">
@@ -54239,12 +54239,12 @@
     <row r="756" ht="16" customHeight="1">
       <c r="A756" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B756" s="10" t="inlineStr">
         <is>
-          <t>PRD-0079</t>
+          <t>PRD-0104</t>
         </is>
       </c>
       <c r="C756" s="9" t="inlineStr">
@@ -54302,12 +54302,12 @@
     <row r="757" ht="16" customHeight="1">
       <c r="A757" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B757" s="16" t="inlineStr">
         <is>
-          <t>PRD-0080</t>
+          <t>PRD-0105</t>
         </is>
       </c>
       <c r="C757" s="15" t="inlineStr">
@@ -54361,12 +54361,12 @@
     <row r="758" ht="16" customHeight="1">
       <c r="A758" s="9" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B758" s="10" t="inlineStr">
         <is>
-          <t>PRD-0081</t>
+          <t>PRD-0106</t>
         </is>
       </c>
       <c r="C758" s="9" t="inlineStr">
@@ -54487,12 +54487,12 @@
     <row r="760" ht="16" customHeight="1">
       <c r="A760" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B760" s="10" t="inlineStr">
         <is>
-          <t>PRD-0083</t>
+          <t>PRD-0107</t>
         </is>
       </c>
       <c r="C760" s="9" t="inlineStr">
@@ -54550,12 +54550,12 @@
     <row r="761" ht="16" customHeight="1">
       <c r="A761" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B761" s="16" t="inlineStr">
         <is>
-          <t>PRD-0084</t>
+          <t>PRD-0108</t>
         </is>
       </c>
       <c r="C761" s="15" t="inlineStr">
@@ -55208,12 +55208,12 @@
     <row r="771" ht="16" customHeight="1">
       <c r="A771" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B771" s="16" t="inlineStr">
         <is>
-          <t>PRD-0094</t>
+          <t>PRD-0109</t>
         </is>
       </c>
       <c r="C771" s="15" t="inlineStr">
@@ -55271,12 +55271,12 @@
     <row r="772" ht="16" customHeight="1">
       <c r="A772" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B772" s="10" t="inlineStr">
         <is>
-          <t>PRD-0095</t>
+          <t>PRD-0110</t>
         </is>
       </c>
       <c r="C772" s="9" t="inlineStr">
@@ -55334,12 +55334,12 @@
     <row r="773" ht="16" customHeight="1">
       <c r="A773" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B773" s="16" t="inlineStr">
         <is>
-          <t>PRD-0096</t>
+          <t>PRD-0111</t>
         </is>
       </c>
       <c r="C773" s="15" t="inlineStr">
@@ -55397,12 +55397,12 @@
     <row r="774" ht="16" customHeight="1">
       <c r="A774" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B774" s="10" t="inlineStr">
         <is>
-          <t>PRD-0097</t>
+          <t>PRD-0112</t>
         </is>
       </c>
       <c r="C774" s="9" t="inlineStr">
@@ -55460,12 +55460,12 @@
     <row r="775" ht="16" customHeight="1">
       <c r="A775" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B775" s="16" t="inlineStr">
         <is>
-          <t>PRD-0098</t>
+          <t>PRD-0113</t>
         </is>
       </c>
       <c r="C775" s="15" t="inlineStr">
@@ -55523,12 +55523,12 @@
     <row r="776" ht="16" customHeight="1">
       <c r="A776" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B776" s="10" t="inlineStr">
         <is>
-          <t>PRD-0099</t>
+          <t>PRD-0114</t>
         </is>
       </c>
       <c r="C776" s="9" t="inlineStr">
@@ -55586,12 +55586,12 @@
     <row r="777" ht="16" customHeight="1">
       <c r="A777" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B777" s="16" t="inlineStr">
         <is>
-          <t>PRD-0100</t>
+          <t>PRD-0115</t>
         </is>
       </c>
       <c r="C777" s="15" t="inlineStr">
@@ -55649,12 +55649,12 @@
     <row r="778" ht="16" customHeight="1">
       <c r="A778" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B778" s="10" t="inlineStr">
         <is>
-          <t>PRD-0101</t>
+          <t>PRD-0116</t>
         </is>
       </c>
       <c r="C778" s="9" t="inlineStr">
@@ -55712,12 +55712,12 @@
     <row r="779" ht="16" customHeight="1">
       <c r="A779" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B779" s="16" t="inlineStr">
         <is>
-          <t>PRD-0102</t>
+          <t>PRD-0117</t>
         </is>
       </c>
       <c r="C779" s="15" t="inlineStr">
@@ -55775,12 +55775,12 @@
     <row r="780" ht="16" customHeight="1">
       <c r="A780" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B780" s="10" t="inlineStr">
         <is>
-          <t>PRD-0103</t>
+          <t>PRD-0118</t>
         </is>
       </c>
       <c r="C780" s="9" t="inlineStr">
@@ -55838,12 +55838,12 @@
     <row r="781" ht="16" customHeight="1">
       <c r="A781" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B781" s="16" t="inlineStr">
         <is>
-          <t>PRD-0104</t>
+          <t>PRD-0119</t>
         </is>
       </c>
       <c r="C781" s="15" t="inlineStr">
@@ -55901,12 +55901,12 @@
     <row r="782" ht="16" customHeight="1">
       <c r="A782" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B782" s="10" t="inlineStr">
         <is>
-          <t>PRD-0105</t>
+          <t>PRD-0120</t>
         </is>
       </c>
       <c r="C782" s="9" t="inlineStr">
@@ -55964,12 +55964,12 @@
     <row r="783" ht="16" customHeight="1">
       <c r="A783" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B783" s="16" t="inlineStr">
         <is>
-          <t>PRD-0106</t>
+          <t>PRD-0121</t>
         </is>
       </c>
       <c r="C783" s="15" t="inlineStr">
@@ -56027,12 +56027,12 @@
     <row r="784" ht="16" customHeight="1">
       <c r="A784" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B784" s="10" t="inlineStr">
         <is>
-          <t>PRD-0107</t>
+          <t>PRD-0122</t>
         </is>
       </c>
       <c r="C784" s="9" t="inlineStr">
@@ -56291,12 +56291,12 @@
     <row r="788" ht="16" customHeight="1">
       <c r="A788" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B788" s="10" t="inlineStr">
         <is>
-          <t>PRD-0111</t>
+          <t>PRD-0123</t>
         </is>
       </c>
       <c r="C788" s="9" t="inlineStr">
@@ -56354,12 +56354,12 @@
     <row r="789" ht="16" customHeight="1">
       <c r="A789" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B789" s="16" t="inlineStr">
         <is>
-          <t>PRD-0112</t>
+          <t>PRD-0124</t>
         </is>
       </c>
       <c r="C789" s="15" t="inlineStr">
@@ -56417,12 +56417,12 @@
     <row r="790" ht="16" customHeight="1">
       <c r="A790" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B790" s="10" t="inlineStr">
         <is>
-          <t>PRD-0113</t>
+          <t>PRD-0125</t>
         </is>
       </c>
       <c r="C790" s="9" t="inlineStr">
@@ -56480,12 +56480,12 @@
     <row r="791" ht="16" customHeight="1">
       <c r="A791" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B791" s="16" t="inlineStr">
         <is>
-          <t>PRD-0114</t>
+          <t>PRD-0126</t>
         </is>
       </c>
       <c r="C791" s="15" t="inlineStr">
@@ -56543,12 +56543,12 @@
     <row r="792" ht="16" customHeight="1">
       <c r="A792" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B792" s="10" t="inlineStr">
         <is>
-          <t>PRD-0115</t>
+          <t>PRD-0127</t>
         </is>
       </c>
       <c r="C792" s="9" t="inlineStr">
@@ -56602,12 +56602,12 @@
     <row r="793" ht="16" customHeight="1">
       <c r="A793" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B793" s="16" t="inlineStr">
         <is>
-          <t>PRD-0116</t>
+          <t>PRD-0128</t>
         </is>
       </c>
       <c r="C793" s="15" t="inlineStr">
@@ -56661,12 +56661,12 @@
     <row r="794" ht="16" customHeight="1">
       <c r="A794" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B794" s="10" t="inlineStr">
         <is>
-          <t>PRD-0117</t>
+          <t>PRD-0129</t>
         </is>
       </c>
       <c r="C794" s="9" t="inlineStr">
@@ -56720,12 +56720,12 @@
     <row r="795" ht="16" customHeight="1">
       <c r="A795" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B795" s="16" t="inlineStr">
         <is>
-          <t>PRD-0118</t>
+          <t>PRD-0130</t>
         </is>
       </c>
       <c r="C795" s="15" t="inlineStr">
@@ -56779,12 +56779,12 @@
     <row r="796" ht="16" customHeight="1">
       <c r="A796" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B796" s="10" t="inlineStr">
         <is>
-          <t>PRD-0119</t>
+          <t>PRD-0131</t>
         </is>
       </c>
       <c r="C796" s="9" t="inlineStr">
@@ -56842,12 +56842,12 @@
     <row r="797" ht="16" customHeight="1">
       <c r="A797" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B797" s="16" t="inlineStr">
         <is>
-          <t>PRD-0120</t>
+          <t>PRD-0132</t>
         </is>
       </c>
       <c r="C797" s="15" t="inlineStr">
@@ -56905,12 +56905,12 @@
     <row r="798" ht="16" customHeight="1">
       <c r="A798" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B798" s="10" t="inlineStr">
         <is>
-          <t>PRD-0121</t>
+          <t>PRD-0133</t>
         </is>
       </c>
       <c r="C798" s="9" t="inlineStr">
@@ -56968,12 +56968,12 @@
     <row r="799" ht="16" customHeight="1">
       <c r="A799" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B799" s="16" t="inlineStr">
         <is>
-          <t>PRD-0122</t>
+          <t>PRD-0134</t>
         </is>
       </c>
       <c r="C799" s="15" t="inlineStr">
@@ -57457,12 +57457,12 @@
     <row r="806" ht="16" customHeight="1">
       <c r="A806" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B806" s="10" t="inlineStr">
         <is>
-          <t>PRD-0129</t>
+          <t>PRD-0135</t>
         </is>
       </c>
       <c r="C806" s="9" t="inlineStr">
@@ -58820,12 +58820,12 @@
     <row r="827" ht="16" customHeight="1">
       <c r="A827" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B827" s="16" t="inlineStr">
         <is>
-          <t>PRD-0150</t>
+          <t>PRD-0136</t>
         </is>
       </c>
       <c r="C827" s="15" t="inlineStr">
@@ -58883,12 +58883,12 @@
     <row r="828" ht="16" customHeight="1">
       <c r="A828" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B828" s="10" t="inlineStr">
         <is>
-          <t>PRD-0151</t>
+          <t>PRD-0137</t>
         </is>
       </c>
       <c r="C828" s="9" t="inlineStr">
@@ -58946,12 +58946,12 @@
     <row r="829" ht="16" customHeight="1">
       <c r="A829" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B829" s="16" t="inlineStr">
         <is>
-          <t>PRD-0152</t>
+          <t>PRD-0138</t>
         </is>
       </c>
       <c r="C829" s="15" t="inlineStr">
@@ -59009,12 +59009,12 @@
     <row r="830" ht="16" customHeight="1">
       <c r="A830" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B830" s="10" t="inlineStr">
         <is>
-          <t>PRD-0153</t>
+          <t>PRD-0139</t>
         </is>
       </c>
       <c r="C830" s="9" t="inlineStr">
@@ -59072,12 +59072,12 @@
     <row r="831" ht="16" customHeight="1">
       <c r="A831" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B831" s="16" t="inlineStr">
         <is>
-          <t>PRD-0154</t>
+          <t>PRD-0140</t>
         </is>
       </c>
       <c r="C831" s="15" t="inlineStr">
@@ -59135,12 +59135,12 @@
     <row r="832" ht="16" customHeight="1">
       <c r="A832" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B832" s="10" t="inlineStr">
         <is>
-          <t>PRD-0155</t>
+          <t>PRD-0141</t>
         </is>
       </c>
       <c r="C832" s="9" t="inlineStr">
@@ -59198,12 +59198,12 @@
     <row r="833" ht="16" customHeight="1">
       <c r="A833" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B833" s="16" t="inlineStr">
         <is>
-          <t>PRD-0156</t>
+          <t>PRD-0142</t>
         </is>
       </c>
       <c r="C833" s="15" t="inlineStr">
@@ -59261,12 +59261,12 @@
     <row r="834" ht="16" customHeight="1">
       <c r="A834" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B834" s="10" t="inlineStr">
         <is>
-          <t>PRD-0157</t>
+          <t>PRD-0143</t>
         </is>
       </c>
       <c r="C834" s="9" t="inlineStr">
@@ -59324,12 +59324,12 @@
     <row r="835" ht="16" customHeight="1">
       <c r="A835" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B835" s="16" t="inlineStr">
         <is>
-          <t>PRD-0158</t>
+          <t>PRD-0144</t>
         </is>
       </c>
       <c r="C835" s="15" t="inlineStr">
@@ -59387,12 +59387,12 @@
     <row r="836" ht="16" customHeight="1">
       <c r="A836" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B836" s="10" t="inlineStr">
         <is>
-          <t>PRD-0159</t>
+          <t>PRD-0145</t>
         </is>
       </c>
       <c r="C836" s="9" t="inlineStr">
@@ -59450,12 +59450,12 @@
     <row r="837" ht="16" customHeight="1">
       <c r="A837" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B837" s="16" t="inlineStr">
         <is>
-          <t>PRD-0160</t>
+          <t>PRD-0146</t>
         </is>
       </c>
       <c r="C837" s="15" t="inlineStr">
@@ -59513,12 +59513,12 @@
     <row r="838" ht="16" customHeight="1">
       <c r="A838" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B838" s="10" t="inlineStr">
         <is>
-          <t>PRD-0161</t>
+          <t>PRD-0147</t>
         </is>
       </c>
       <c r="C838" s="9" t="inlineStr">
@@ -59576,12 +59576,12 @@
     <row r="839" ht="16" customHeight="1">
       <c r="A839" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B839" s="16" t="inlineStr">
         <is>
-          <t>PRD-0162</t>
+          <t>PRD-0148</t>
         </is>
       </c>
       <c r="C839" s="15" t="inlineStr">
@@ -59639,12 +59639,12 @@
     <row r="840" ht="16" customHeight="1">
       <c r="A840" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B840" s="10" t="inlineStr">
         <is>
-          <t>PRD-0163</t>
+          <t>PRD-0149</t>
         </is>
       </c>
       <c r="C840" s="9" t="inlineStr">
@@ -59966,12 +59966,12 @@
     <row r="845" ht="16" customHeight="1">
       <c r="A845" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B845" s="16" t="inlineStr">
         <is>
-          <t>PRD-0168</t>
+          <t>PRD-0150</t>
         </is>
       </c>
       <c r="C845" s="15" t="inlineStr">
@@ -60025,12 +60025,12 @@
     <row r="846" ht="16" customHeight="1">
       <c r="A846" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B846" s="10" t="inlineStr">
         <is>
-          <t>PRD-0169</t>
+          <t>PRD-0151</t>
         </is>
       </c>
       <c r="C846" s="9" t="inlineStr">
@@ -60088,12 +60088,12 @@
     <row r="847" ht="16" customHeight="1">
       <c r="A847" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B847" s="16" t="inlineStr">
         <is>
-          <t>PRD-0170</t>
+          <t>PRD-0152</t>
         </is>
       </c>
       <c r="C847" s="15" t="inlineStr">
@@ -60151,12 +60151,12 @@
     <row r="848" ht="16" customHeight="1">
       <c r="A848" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B848" s="10" t="inlineStr">
         <is>
-          <t>PRD-0171</t>
+          <t>PRD-0153</t>
         </is>
       </c>
       <c r="C848" s="9" t="inlineStr">
@@ -60214,12 +60214,12 @@
     <row r="849" ht="16" customHeight="1">
       <c r="A849" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B849" s="16" t="inlineStr">
         <is>
-          <t>PRD-0172</t>
+          <t>PRD-0154</t>
         </is>
       </c>
       <c r="C849" s="15" t="inlineStr">
@@ -60277,12 +60277,12 @@
     <row r="850" ht="16" customHeight="1">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B850" s="10" t="inlineStr">
         <is>
-          <t>PRD-0173</t>
+          <t>PRD-0155</t>
         </is>
       </c>
       <c r="C850" s="9" t="inlineStr">
@@ -60340,12 +60340,12 @@
     <row r="851" ht="16" customHeight="1">
       <c r="A851" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B851" s="16" t="inlineStr">
         <is>
-          <t>PRD-0174</t>
+          <t>PRD-0156</t>
         </is>
       </c>
       <c r="C851" s="15" t="inlineStr">
@@ -60403,12 +60403,12 @@
     <row r="852" ht="16" customHeight="1">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B852" s="10" t="inlineStr">
         <is>
-          <t>PRD-0175</t>
+          <t>PRD-0157</t>
         </is>
       </c>
       <c r="C852" s="9" t="inlineStr">
@@ -60466,12 +60466,12 @@
     <row r="853" ht="16" customHeight="1">
       <c r="A853" s="15" t="inlineStr">
         <is>
-          <t>Kit/Assay</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B853" s="16" t="inlineStr">
         <is>
-          <t>PRD-0176</t>
+          <t>PRD-0158</t>
         </is>
       </c>
       <c r="C853" s="15" t="inlineStr">
@@ -60529,12 +60529,12 @@
     <row r="854" ht="16" customHeight="1">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B854" s="10" t="inlineStr">
         <is>
-          <t>PRD-0177</t>
+          <t>PRD-0159</t>
         </is>
       </c>
       <c r="C854" s="9" t="inlineStr">
@@ -60592,12 +60592,12 @@
     <row r="855" ht="16" customHeight="1">
       <c r="A855" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B855" s="16" t="inlineStr">
         <is>
-          <t>PRD-0178</t>
+          <t>PRD-0160</t>
         </is>
       </c>
       <c r="C855" s="15" t="inlineStr">
@@ -60718,12 +60718,12 @@
     <row r="857" ht="16" customHeight="1">
       <c r="A857" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B857" s="16" t="inlineStr">
         <is>
-          <t>PRD-0180</t>
+          <t>PRD-0161</t>
         </is>
       </c>
       <c r="C857" s="15" t="inlineStr">
@@ -60781,12 +60781,12 @@
     <row r="858" ht="16" customHeight="1">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B858" s="10" t="inlineStr">
         <is>
-          <t>PRD-0181</t>
+          <t>PRD-0162</t>
         </is>
       </c>
       <c r="C858" s="9" t="inlineStr">
@@ -60844,12 +60844,12 @@
     <row r="859" ht="16" customHeight="1">
       <c r="A859" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B859" s="16" t="inlineStr">
         <is>
-          <t>PRD-0182</t>
+          <t>PRD-0163</t>
         </is>
       </c>
       <c r="C859" s="15" t="inlineStr">
@@ -60907,12 +60907,12 @@
     <row r="860" ht="16" customHeight="1">
       <c r="A860" s="9" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B860" s="10" t="inlineStr">
         <is>
-          <t>PRD-0183</t>
+          <t>PRD-0164</t>
         </is>
       </c>
       <c r="C860" s="9" t="inlineStr">
@@ -60970,12 +60970,12 @@
     <row r="861" ht="16" customHeight="1">
       <c r="A861" s="15" t="inlineStr">
         <is>
-          <t>Cell Culture</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B861" s="16" t="inlineStr">
         <is>
-          <t>PRD-0184</t>
+          <t>PRD-0165</t>
         </is>
       </c>
       <c r="C861" s="15" t="inlineStr">
@@ -61037,12 +61037,12 @@
     <row r="862" ht="16" customHeight="1">
       <c r="A862" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B862" s="10" t="inlineStr">
         <is>
-          <t>PRD-0185</t>
+          <t>PRD-0166</t>
         </is>
       </c>
       <c r="C862" s="9" t="inlineStr">
@@ -61100,12 +61100,12 @@
     <row r="863" ht="16" customHeight="1">
       <c r="A863" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B863" s="16" t="inlineStr">
         <is>
-          <t>PRD-0186</t>
+          <t>PRD-0167</t>
         </is>
       </c>
       <c r="C863" s="15" t="inlineStr">
@@ -61163,12 +61163,12 @@
     <row r="864" ht="16" customHeight="1">
       <c r="A864" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B864" s="10" t="inlineStr">
         <is>
-          <t>PRD-0187</t>
+          <t>PRD-0168</t>
         </is>
       </c>
       <c r="C864" s="9" t="inlineStr">
@@ -61226,12 +61226,12 @@
     <row r="865" ht="16" customHeight="1">
       <c r="A865" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B865" s="16" t="inlineStr">
         <is>
-          <t>PRD-0188</t>
+          <t>PRD-0169</t>
         </is>
       </c>
       <c r="C865" s="15" t="inlineStr">
@@ -61289,12 +61289,12 @@
     <row r="866" ht="16" customHeight="1">
       <c r="A866" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B866" s="10" t="inlineStr">
         <is>
-          <t>PRD-0189</t>
+          <t>PRD-0170</t>
         </is>
       </c>
       <c r="C866" s="9" t="inlineStr">
@@ -61352,12 +61352,12 @@
     <row r="867" ht="16" customHeight="1">
       <c r="A867" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B867" s="16" t="inlineStr">
         <is>
-          <t>PRD-0190</t>
+          <t>PRD-0171</t>
         </is>
       </c>
       <c r="C867" s="15" t="inlineStr">
@@ -61415,12 +61415,12 @@
     <row r="868" ht="16" customHeight="1">
       <c r="A868" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B868" s="10" t="inlineStr">
         <is>
-          <t>PRD-0191</t>
+          <t>PRD-0172</t>
         </is>
       </c>
       <c r="C868" s="9" t="inlineStr">
@@ -61478,12 +61478,12 @@
     <row r="869" ht="16" customHeight="1">
       <c r="A869" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B869" s="16" t="inlineStr">
         <is>
-          <t>PRD-0192</t>
+          <t>PRD-0173</t>
         </is>
       </c>
       <c r="C869" s="15" t="inlineStr">
@@ -61817,12 +61817,12 @@
     <row r="874" ht="16" customHeight="1">
       <c r="A874" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B874" s="10" t="inlineStr">
         <is>
-          <t>PRD-0197</t>
+          <t>PRD-0174</t>
         </is>
       </c>
       <c r="C874" s="9" t="inlineStr">
@@ -61880,12 +61880,12 @@
     <row r="875" ht="16" customHeight="1">
       <c r="A875" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B875" s="16" t="inlineStr">
         <is>
-          <t>PRD-0198</t>
+          <t>PRD-0175</t>
         </is>
       </c>
       <c r="C875" s="15" t="inlineStr">
@@ -61943,12 +61943,12 @@
     <row r="876" ht="16" customHeight="1">
       <c r="A876" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B876" s="10" t="inlineStr">
         <is>
-          <t>PRD-0199</t>
+          <t>PRD-0176</t>
         </is>
       </c>
       <c r="C876" s="9" t="inlineStr">
@@ -62006,12 +62006,12 @@
     <row r="877" ht="16" customHeight="1">
       <c r="A877" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B877" s="16" t="inlineStr">
         <is>
-          <t>PRD-0200</t>
+          <t>PRD-0177</t>
         </is>
       </c>
       <c r="C877" s="15" t="inlineStr">
@@ -62069,12 +62069,12 @@
     <row r="878" ht="16" customHeight="1">
       <c r="A878" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B878" s="10" t="inlineStr">
         <is>
-          <t>PRD-0201</t>
+          <t>PRD-0178</t>
         </is>
       </c>
       <c r="C878" s="9" t="inlineStr">
@@ -62132,12 +62132,12 @@
     <row r="879" ht="16" customHeight="1">
       <c r="A879" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B879" s="16" t="inlineStr">
         <is>
-          <t>PRD-0202</t>
+          <t>PRD-0179</t>
         </is>
       </c>
       <c r="C879" s="15" t="inlineStr">
@@ -62191,12 +62191,12 @@
     <row r="880" ht="16" customHeight="1">
       <c r="A880" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B880" s="10" t="inlineStr">
         <is>
-          <t>PRD-0203</t>
+          <t>PRD-0180</t>
         </is>
       </c>
       <c r="C880" s="9" t="inlineStr">
@@ -62254,12 +62254,12 @@
     <row r="881" ht="16" customHeight="1">
       <c r="A881" s="15" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B881" s="16" t="inlineStr">
         <is>
-          <t>PRD-0204</t>
+          <t>PRD-0181</t>
         </is>
       </c>
       <c r="C881" s="15" t="inlineStr">
@@ -62317,12 +62317,12 @@
     <row r="882" ht="16" customHeight="1">
       <c r="A882" s="9" t="inlineStr">
         <is>
-          <t>Consumable</t>
+          <t>Products</t>
         </is>
       </c>
       <c r="B882" s="10" t="inlineStr">
         <is>
-          <t>PRD-0205</t>
+          <t>PRD-0182</t>
         </is>
       </c>
       <c r="C882" s="9" t="inlineStr">
